--- a/Business - Technology Services/NBIS.xlsx
+++ b/Business - Technology Services/NBIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\Business - Technology Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDE5261-2C03-433A-A0AB-ED1DBB6C1CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702369DC-E23B-48A6-B912-8D200874FCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="45" windowWidth="15120" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1685,7 +1685,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1836,6 +1836,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1871,14 +1875,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -15492,7 +15488,7 @@
       <c r="E3" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F3" s="141">
+      <c r="F3" s="125">
         <v>9.6299999999999997E-2</v>
       </c>
       <c r="I3" s="10"/>
@@ -15513,7 +15509,7 @@
       <c r="E4" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F4" s="141">
+      <c r="F4" s="125">
         <v>5.8700000000000002E-2</v>
       </c>
       <c r="I4" s="10"/>
@@ -15754,11 +15750,11 @@
       <c r="E17" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="L17" s="124" t="s">
+      <c r="L17" s="126" t="s">
         <v>163</v>
       </c>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
@@ -15771,9 +15767,9 @@
       <c r="E18" t="s">
         <v>162</v>
       </c>
-      <c r="L18" s="125"/>
-      <c r="M18" s="125"/>
-      <c r="N18" s="125"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="127"/>
+      <c r="N18" s="127"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
@@ -15783,9 +15779,9 @@
         <f>C15/(C17*100)</f>
         <v>0.2681475805307223</v>
       </c>
-      <c r="L19" s="125"/>
-      <c r="M19" s="125"/>
-      <c r="N19" s="125"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="127"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -15795,9 +15791,9 @@
         <f>Model!F7/Model!E7-1</f>
         <v>3.9205106382978725</v>
       </c>
-      <c r="L20" s="125"/>
-      <c r="M20" s="125"/>
-      <c r="N20" s="125"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="127"/>
+      <c r="N20" s="127"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
@@ -15807,9 +15803,9 @@
         <f>Model!G7/Model!F7-1</f>
         <v>1.9057700290577007</v>
       </c>
-      <c r="L21" s="125"/>
-      <c r="M21" s="125"/>
-      <c r="N21" s="125"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="127"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
@@ -15819,9 +15815,9 @@
         <f>Model!C13+Model!C11</f>
         <v>0</v>
       </c>
-      <c r="L22" s="125"/>
-      <c r="M22" s="125"/>
-      <c r="N22" s="125"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="127"/>
+      <c r="N22" s="127"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
@@ -15831,9 +15827,9 @@
         <f>Model!C13</f>
         <v>0</v>
       </c>
-      <c r="L23" s="125"/>
-      <c r="M23" s="125"/>
-      <c r="N23" s="125"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="127"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
@@ -15843,9 +15839,9 @@
         <f>Model!C17</f>
         <v>0</v>
       </c>
-      <c r="L24" s="125"/>
-      <c r="M24" s="125"/>
-      <c r="N24" s="125"/>
+      <c r="L24" s="127"/>
+      <c r="M24" s="127"/>
+      <c r="N24" s="127"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
@@ -15855,18 +15851,18 @@
         <f>Model!C18</f>
         <v>0</v>
       </c>
-      <c r="L25" s="125"/>
-      <c r="M25" s="125"/>
-      <c r="N25" s="125"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C26" s="36"/>
-      <c r="L26" s="125"/>
-      <c r="M26" s="125"/>
-      <c r="N26" s="125"/>
+      <c r="L26" s="127"/>
+      <c r="M26" s="127"/>
+      <c r="N26" s="127"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
@@ -15879,9 +15875,9 @@
       <c r="E27" t="s">
         <v>59</v>
       </c>
-      <c r="L27" s="125"/>
-      <c r="M27" s="125"/>
-      <c r="N27" s="125"/>
+      <c r="L27" s="127"/>
+      <c r="M27" s="127"/>
+      <c r="N27" s="127"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
@@ -15894,9 +15890,9 @@
       <c r="E28" t="s">
         <v>188</v>
       </c>
-      <c r="L28" s="125"/>
-      <c r="M28" s="125"/>
-      <c r="N28" s="125"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="127"/>
+      <c r="N28" s="127"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
@@ -15909,9 +15905,9 @@
       <c r="E29" t="s">
         <v>189</v>
       </c>
-      <c r="L29" s="125"/>
-      <c r="M29" s="125"/>
-      <c r="N29" s="125"/>
+      <c r="L29" s="127"/>
+      <c r="M29" s="127"/>
+      <c r="N29" s="127"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
@@ -15924,9 +15920,9 @@
       <c r="E30" t="s">
         <v>190</v>
       </c>
-      <c r="L30" s="125"/>
-      <c r="M30" s="125"/>
-      <c r="N30" s="125"/>
+      <c r="L30" s="127"/>
+      <c r="M30" s="127"/>
+      <c r="N30" s="127"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
@@ -15936,18 +15932,18 @@
         <f>(Model!E46-Model!E59)/Model!E54</f>
         <v>0.63949163050216984</v>
       </c>
-      <c r="L31" s="125"/>
-      <c r="M31" s="125"/>
-      <c r="N31" s="125"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="127"/>
+      <c r="N31" s="127"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="36"/>
-      <c r="L32" s="125"/>
-      <c r="M32" s="125"/>
-      <c r="N32" s="125"/>
+      <c r="L32" s="127"/>
+      <c r="M32" s="127"/>
+      <c r="N32" s="127"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
@@ -16105,7 +16101,6 @@
       <c r="M4">
         <v>0.1</v>
       </c>
-      <c r="P4" s="136"/>
       <c r="Q4" s="13">
         <v>0.2</v>
       </c>
@@ -16119,7 +16114,6 @@
       <c r="M5">
         <v>6.3</v>
       </c>
-      <c r="P5" s="136"/>
       <c r="Q5" s="13">
         <v>16.2</v>
       </c>
@@ -16133,7 +16127,6 @@
       <c r="M6">
         <v>-1.4</v>
       </c>
-      <c r="P6" s="136"/>
       <c r="Q6" s="13">
         <v>-1.4</v>
       </c>
@@ -16182,7 +16175,7 @@
         <f t="shared" si="2"/>
         <v>55.3</v>
       </c>
-      <c r="P7" s="137">
+      <c r="P7" s="11">
         <f t="shared" si="2"/>
         <v>105.1</v>
       </c>
@@ -16221,7 +16214,7 @@
       <c r="M8" s="40"/>
       <c r="N8" s="40"/>
       <c r="O8" s="40"/>
-      <c r="P8" s="138"/>
+      <c r="P8" s="40"/>
       <c r="Q8" s="13">
         <v>155.72</v>
       </c>
@@ -16255,7 +16248,7 @@
       <c r="O9" s="40">
         <v>29.5</v>
       </c>
-      <c r="P9" s="138">
+      <c r="P9" s="40">
         <v>30.1</v>
       </c>
       <c r="Q9" s="13">
@@ -16276,7 +16269,7 @@
       <c r="M10" s="40"/>
       <c r="N10" s="40"/>
       <c r="O10" s="40"/>
-      <c r="P10" s="138"/>
+      <c r="P10" s="40"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -16292,7 +16285,7 @@
       <c r="M11" s="40"/>
       <c r="N11" s="40"/>
       <c r="O11" s="40"/>
-      <c r="P11" s="138"/>
+      <c r="P11" s="40"/>
     </row>
     <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -16338,7 +16331,7 @@
         <f t="shared" si="5"/>
         <v>29.5</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="11">
         <f t="shared" si="5"/>
         <v>30.1</v>
       </c>
@@ -16384,7 +16377,7 @@
       <c r="O13" s="10">
         <v>40</v>
       </c>
-      <c r="P13" s="139">
+      <c r="P13" s="10">
         <v>42.8</v>
       </c>
       <c r="Q13" s="13">
@@ -16416,7 +16409,7 @@
       <c r="O14" s="10">
         <v>66.099999999999994</v>
       </c>
-      <c r="P14" s="139">
+      <c r="P14" s="10">
         <v>68.2</v>
       </c>
       <c r="Q14" s="13">
@@ -16448,7 +16441,7 @@
       <c r="O15" s="10">
         <v>49.2</v>
       </c>
-      <c r="P15" s="139">
+      <c r="P15" s="10">
         <v>75.2</v>
       </c>
       <c r="Q15" s="13">
@@ -16909,7 +16902,7 @@
         <v>-0.47496652022156877</v>
       </c>
       <c r="R25" s="2" t="e">
-        <f t="shared" ref="Q25:T25" si="20">R23/R24</f>
+        <f t="shared" ref="R25:T25" si="20">R23/R24</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S25" s="2" t="e">
@@ -17115,7 +17108,7 @@
         <f t="shared" si="23"/>
         <v>6.2482758620689651</v>
       </c>
-      <c r="Q29" s="140">
+      <c r="Q29" s="124">
         <f t="shared" si="23"/>
         <v>3.5514018691588776</v>
       </c>
@@ -17271,19 +17264,19 @@
         <v>#REF!</v>
       </c>
       <c r="D32" s="4" t="e">
-        <f>D3/C3-1</f>
+        <f t="shared" ref="D32:G33" si="26">D3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E32" s="7" t="e">
-        <f>E3/D3-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F32" s="4">
-        <f>F3/E3-1</f>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="G32" s="4" t="e">
-        <f>G3/F3-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K32" s="4"/>
@@ -17306,19 +17299,19 @@
         <v>#REF!</v>
       </c>
       <c r="D33" s="4" t="e">
-        <f>D4/C4-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="7" t="e">
-        <f>E4/D4-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F33" s="4" t="e">
-        <f>F4/E4-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="4" t="e">
-        <f>G4/F4-1</f>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="4"/>
@@ -17361,27 +17354,27 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4">
-        <f t="shared" ref="O34:T34" si="26">O23/K23-1</f>
+        <f t="shared" ref="O34:T34" si="27">O23/K23-1</f>
         <v>-0.64107424960505521</v>
       </c>
       <c r="P34" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-7.012345679012344</v>
       </c>
       <c r="Q34" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.7431192660550474</v>
       </c>
       <c r="R34" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="S34" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="T34" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
     </row>
@@ -17452,63 +17445,63 @@
         <v>26</v>
       </c>
       <c r="C39" s="11">
-        <f t="shared" ref="C39:G39" si="27">C40-C56</f>
+        <f t="shared" ref="C39:G39" si="28">C40-C56</f>
         <v>0</v>
       </c>
       <c r="D39" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>109.3</v>
       </c>
       <c r="E39" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2443.5</v>
       </c>
       <c r="F39" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="G39" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K39" s="11">
-        <f t="shared" ref="K39" si="28">K40-K56</f>
+        <f t="shared" ref="K39" si="29">K40-K56</f>
         <v>0</v>
       </c>
       <c r="L39" s="11">
-        <f t="shared" ref="L39" si="29">L40-L56</f>
+        <f t="shared" ref="L39" si="30">L40-L56</f>
         <v>0</v>
       </c>
       <c r="M39" s="11">
-        <f t="shared" ref="M39" si="30">M40-M56</f>
+        <f t="shared" ref="M39" si="31">M40-M56</f>
         <v>0</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" ref="N39" si="31">N40-N56</f>
+        <f t="shared" ref="N39" si="32">N40-N56</f>
         <v>2443.5</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" ref="O39" si="32">O40-O56</f>
+        <f t="shared" ref="O39" si="33">O40-O56</f>
         <v>1440.8</v>
       </c>
       <c r="P39" s="11">
-        <f t="shared" ref="P39" si="33">P40-P56</f>
+        <f t="shared" ref="P39" si="34">P40-P56</f>
         <v>1671.3</v>
       </c>
       <c r="Q39" s="11">
-        <f t="shared" ref="Q39" si="34">Q40-Q56</f>
+        <f t="shared" ref="Q39" si="35">Q40-Q56</f>
         <v>4778.8</v>
       </c>
       <c r="R39" s="11">
-        <f t="shared" ref="R39" si="35">R40-R56</f>
+        <f t="shared" ref="R39" si="36">R40-R56</f>
         <v>0</v>
       </c>
       <c r="S39" s="11">
-        <f t="shared" ref="S39" si="36">S40-S56</f>
+        <f t="shared" ref="S39" si="37">S40-S56</f>
         <v>0</v>
       </c>
       <c r="T39" s="11">
-        <f t="shared" ref="T39" si="37">T40-T56</f>
+        <f t="shared" ref="T39" si="38">T40-T56</f>
         <v>0</v>
       </c>
     </row>
@@ -17558,7 +17551,7 @@
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <f t="shared" ref="N41:N45" si="38">E41</f>
+        <f t="shared" ref="N41:N45" si="39">E41</f>
         <v>13.1</v>
       </c>
       <c r="O41" s="10">
@@ -17589,7 +17582,7 @@
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>22.9</v>
       </c>
       <c r="O42" s="10">
@@ -17620,7 +17613,7 @@
       <c r="L43" s="10"/>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.6</v>
       </c>
       <c r="O43" s="10">
@@ -17651,7 +17644,7 @@
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>8.1</v>
       </c>
       <c r="O44" s="10">
@@ -17683,7 +17676,7 @@
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>39</v>
       </c>
       <c r="O45" s="10">
@@ -17704,63 +17697,63 @@
         <v>46</v>
       </c>
       <c r="C46" s="11">
-        <f t="shared" ref="C46:D46" si="39">SUM(C40:C45)</f>
+        <f t="shared" ref="C46:D46" si="40">SUM(C40:C45)</f>
         <v>0</v>
       </c>
       <c r="D46" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3455.9</v>
       </c>
       <c r="E46" s="14">
-        <f t="shared" ref="E46:G46" si="40">SUM(E40:E45)</f>
+        <f t="shared" ref="E46:G46" si="41">SUM(E40:E45)</f>
         <v>2533.2999999999997</v>
       </c>
       <c r="F46" s="11">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="11">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="11">
-        <f t="shared" ref="K46:M46" si="41">SUM(K40:K45)</f>
-        <v>0</v>
-      </c>
-      <c r="L46" s="11">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="M46" s="11">
+      <c r="G46" s="11">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
+      <c r="K46" s="11">
+        <f t="shared" ref="K46:M46" si="42">SUM(K40:K45)</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="11">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="11">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
       <c r="N46" s="11">
-        <f t="shared" ref="N46:P46" si="42">SUM(N40:N45)</f>
+        <f t="shared" ref="N46:P46" si="43">SUM(N40:N45)</f>
         <v>2533.2999999999997</v>
       </c>
       <c r="O46" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1683.3</v>
       </c>
       <c r="P46" s="11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2029.6</v>
       </c>
       <c r="Q46" s="14">
-        <f t="shared" ref="Q46:T46" si="43">SUM(Q40:Q45)</f>
+        <f t="shared" ref="Q46:T46" si="44">SUM(Q40:Q45)</f>
         <v>5217</v>
       </c>
       <c r="R46" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="S46" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="T46" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
@@ -17781,7 +17774,7 @@
       <c r="L47" s="10"/>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <f t="shared" ref="N47:N53" si="44">E47</f>
+        <f t="shared" ref="N47:N53" si="45">E47</f>
         <v>847</v>
       </c>
       <c r="O47" s="10">
@@ -17814,7 +17807,7 @@
       <c r="L48" s="10"/>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>4.9000000000000004</v>
       </c>
       <c r="O48" s="10">
@@ -17847,7 +17840,7 @@
       <c r="L49" s="10"/>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>45</v>
       </c>
       <c r="O49" s="10">
@@ -17880,7 +17873,7 @@
       <c r="L50" s="10"/>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>6.4</v>
       </c>
       <c r="O50" s="10">
@@ -17913,7 +17906,7 @@
       <c r="L51" s="10"/>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>90.7</v>
       </c>
       <c r="O51" s="10">
@@ -17946,7 +17939,7 @@
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>7.8</v>
       </c>
       <c r="O52" s="10">
@@ -17980,7 +17973,7 @@
       <c r="L53" s="10"/>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>13.5</v>
       </c>
       <c r="O53" s="10">
@@ -18021,43 +18014,43 @@
         <v>0</v>
       </c>
       <c r="K54" s="11">
-        <f t="shared" ref="K54:T54" si="45">SUM(K46:K53)</f>
+        <f t="shared" ref="K54:T54" si="46">SUM(K46:K53)</f>
         <v>0</v>
       </c>
       <c r="L54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="N54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>3548.6</v>
       </c>
       <c r="O54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>3436.5</v>
       </c>
       <c r="P54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>5096.6000000000004</v>
       </c>
       <c r="Q54" s="14">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>10102.200000000001</v>
       </c>
       <c r="R54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="S54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="T54" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
     </row>
@@ -18078,7 +18071,7 @@
       <c r="L55" s="10"/>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <f t="shared" ref="N55:N58" si="46">E55</f>
+        <f t="shared" ref="N55:N58" si="47">E55</f>
         <v>235.5</v>
       </c>
       <c r="O55" s="10">
@@ -18111,7 +18104,7 @@
       <c r="L56" s="10"/>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>6.1</v>
       </c>
       <c r="O56" s="10">
@@ -18144,7 +18137,7 @@
       <c r="L57" s="10"/>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.9</v>
       </c>
       <c r="O57" s="10">
@@ -18178,7 +18171,7 @@
       <c r="L58" s="10"/>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>16.5</v>
       </c>
       <c r="O58" s="10">
@@ -18219,43 +18212,43 @@
         <v>0</v>
       </c>
       <c r="K59" s="11">
-        <f t="shared" ref="K59:T59" si="47">SUM(K55:K58)</f>
+        <f t="shared" ref="K59:T59" si="48">SUM(K55:K58)</f>
         <v>0</v>
       </c>
       <c r="L59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="N59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>264</v>
       </c>
       <c r="O59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>93.5</v>
       </c>
       <c r="P59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>138.1</v>
       </c>
       <c r="Q59" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>794.6</v>
       </c>
       <c r="R59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="S59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="T59" s="11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
     </row>
@@ -18276,7 +18269,7 @@
       <c r="L60" s="10"/>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
-        <f t="shared" ref="N60:N62" si="48">E60</f>
+        <f t="shared" ref="N60:N62" si="49">E60</f>
         <v>30.3</v>
       </c>
       <c r="O60" s="10">
@@ -18332,7 +18325,7 @@
       <c r="L62" s="10"/>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.6</v>
       </c>
       <c r="O62" s="10">
@@ -18374,43 +18367,43 @@
         <v>0</v>
       </c>
       <c r="K63" s="11">
-        <f t="shared" ref="K63:T63" si="49">SUM(K59:K62)</f>
+        <f t="shared" ref="K63:T63" si="50">SUM(K59:K62)</f>
         <v>0</v>
       </c>
       <c r="L63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="N63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>294.90000000000003</v>
       </c>
       <c r="O63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>275.20000000000005</v>
       </c>
       <c r="P63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1321.1</v>
       </c>
       <c r="Q63" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5291.4000000000005</v>
       </c>
       <c r="R63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="S63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="T63" s="11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
@@ -18439,43 +18432,43 @@
         <v>0</v>
       </c>
       <c r="K64" s="10">
-        <f t="shared" ref="K64:T64" si="50">K54-K63</f>
+        <f t="shared" ref="K64:T64" si="51">K54-K63</f>
         <v>0</v>
       </c>
       <c r="L64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="N64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3253.7</v>
       </c>
       <c r="O64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3161.3</v>
       </c>
       <c r="P64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3775.5000000000005</v>
       </c>
       <c r="Q64" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4810.8</v>
       </c>
       <c r="R64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="S64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="T64" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
     </row>
@@ -27059,14 +27052,14 @@
       <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="126" t="s">
+      <c r="H1" s="128" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="128"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="130"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" t="e">
@@ -27473,10 +27466,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="129" t="s">
+      <c r="H17" s="131" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="130"/>
+      <c r="I17" s="132"/>
       <c r="M17" s="77"/>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.25">
@@ -27484,8 +27477,8 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="131"/>
-      <c r="I18" s="132"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="134"/>
       <c r="M18" s="77"/>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.25">
@@ -27908,14 +27901,14 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H43" s="133" t="s">
+      <c r="H43" s="135" t="s">
         <v>113</v>
       </c>
-      <c r="I43" s="134"/>
-      <c r="J43" s="134"/>
-      <c r="K43" s="134"/>
-      <c r="L43" s="134"/>
-      <c r="M43" s="135"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="136"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
+      <c r="M43" s="137"/>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D44" t="e">

--- a/Business - Technology Services/NBIS.xlsx
+++ b/Business - Technology Services/NBIS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\Business - Technology Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702369DC-E23B-48A6-B912-8D200874FCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF6C535-01C6-405B-A48A-04C4A150F67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15105" yWindow="0" windowWidth="13800" windowHeight="15585" tabRatio="739" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="200">
   <si>
     <t>Price</t>
   </si>
@@ -532,12 +532,6 @@
   </si>
   <si>
     <t>Equity</t>
-  </si>
-  <si>
-    <t>Interest exp / REV</t>
-  </si>
-  <si>
-    <t>Interest exp / op Inc</t>
   </si>
   <si>
     <t>Interest Rate debt</t>
@@ -937,6 +931,18 @@
   <si>
     <t>Altshuler Shaman Ltd</t>
   </si>
+  <si>
+    <t>Close of Deals with Hyperscalers (META, MSFT)</t>
+  </si>
+  <si>
+    <t>Investments of Nvidia into the company</t>
+  </si>
+  <si>
+    <t>CapEX Spending from Hyperscalers</t>
+  </si>
+  <si>
+    <t>FY27</t>
+  </si>
 </sst>
 </file>
 
@@ -1056,7 +1062,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1090,12 +1096,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9B9B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1683,9 +1683,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1732,14 +1732,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1750,121 +1745,118 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="11" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="12" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="12" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="10" fillId="9" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="10" fillId="9" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="9" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1876,6 +1868,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -4688,10 +4696,10 @@
                   <c:v>117.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>578.16</c:v>
+                  <c:v>534.19999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1680</c:v>
+                  <c:v>3330</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4823,10 +4831,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9205106382978725</c:v>
+                  <c:v>3.546382978723404</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.9057700290577007</c:v>
+                  <c:v>5.2336203669037822</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5864,7 +5872,7 @@
                   <c:v>-2.7342106334749503</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.41400185401928724</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -5988,7 +5996,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>-1.1514154940920283</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -7081,7 +7089,7 @@
                   <c:v>1.1038297872340423</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.33845001871958069</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -7231,7 +7239,7 @@
                   <c:v>2.3642553191489362</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.71827031074503944</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15455,7 +15463,7 @@
       <c r="E2" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="48" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="25"/>
@@ -15486,18 +15494,18 @@
         <v>45967</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" s="125">
+        <v>190</v>
+      </c>
+      <c r="F3" s="117">
         <v>9.6299999999999997E-2</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="38"/>
       <c r="L3" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N3" s="37"/>
     </row>
@@ -15507,18 +15515,18 @@
         <v>0.81111111111111112</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F4" s="125">
+        <v>191</v>
+      </c>
+      <c r="F4" s="117">
         <v>5.8700000000000002E-2</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="38"/>
       <c r="L4" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N4" s="13"/>
     </row>
@@ -15526,7 +15534,7 @@
       <c r="B5" s="5"/>
       <c r="C5" s="13"/>
       <c r="E5" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F5" s="28">
         <v>4.6399999999999997</v>
@@ -15534,10 +15542,10 @@
       <c r="I5" s="10"/>
       <c r="J5" s="38"/>
       <c r="L5" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N5" s="13"/>
     </row>
@@ -15546,10 +15554,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="16">
-        <v>96.41</v>
+        <v>129.85</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F6" s="28">
         <v>2.11</v>
@@ -15557,10 +15565,10 @@
       <c r="I6" s="10"/>
       <c r="J6" s="38"/>
       <c r="L6" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N6" s="13"/>
     </row>
@@ -15569,11 +15577,11 @@
         <v>1</v>
       </c>
       <c r="C7" s="15">
-        <f>Model!P24</f>
-        <v>238.70509200000001</v>
+        <f>Model!R24</f>
+        <v>253.01697100000001</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F7" s="28">
         <v>2.1</v>
@@ -15581,10 +15589,10 @@
       <c r="I7" s="10"/>
       <c r="J7" s="38"/>
       <c r="L7" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N7" s="13"/>
     </row>
@@ -15594,10 +15602,10 @@
       </c>
       <c r="C8" s="15">
         <f>C6*C7</f>
-        <v>23013.557919719999</v>
+        <v>32854.253684349998</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F8" s="28">
         <v>1.92</v>
@@ -15605,10 +15613,10 @@
       <c r="I8" s="10"/>
       <c r="J8" s="38"/>
       <c r="L8" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N8" s="13"/>
     </row>
@@ -15617,18 +15625,18 @@
         <v>3</v>
       </c>
       <c r="C9" s="15">
-        <f>Model!P40</f>
-        <v>1679.3</v>
+        <f>Model!R39</f>
+        <v>3678.1</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="28"/>
       <c r="I9" s="10"/>
       <c r="J9" s="38"/>
       <c r="L9" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N9" s="13"/>
     </row>
@@ -15637,18 +15645,18 @@
         <v>4</v>
       </c>
       <c r="C10" s="15">
-        <f>Model!P56</f>
-        <v>8</v>
+        <f>Model!R55+Model!R60</f>
+        <v>4127.7</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="28"/>
       <c r="I10" s="10"/>
       <c r="J10" s="38"/>
       <c r="L10" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N10" s="13"/>
     </row>
@@ -15658,17 +15666,17 @@
       </c>
       <c r="C11" s="15">
         <f>C9-C10</f>
-        <v>1671.3</v>
+        <v>-449.59999999999991</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="28"/>
       <c r="I11" s="10"/>
       <c r="J11" s="38"/>
       <c r="L11" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N11" s="13"/>
     </row>
@@ -15678,16 +15686,16 @@
       </c>
       <c r="C12" s="15">
         <f>C8-C9+C10</f>
-        <v>21342.257919719999</v>
+        <v>33303.853684349997</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="28"/>
       <c r="J12" s="13"/>
       <c r="L12" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N12" s="13"/>
     </row>
@@ -15696,8 +15704,8 @@
         <v>33</v>
       </c>
       <c r="C13" s="36">
-        <f>C6/Model!E25</f>
-        <v>-35.260633844244488</v>
+        <f>C6/Model!F25</f>
+        <v>313.64593839222425</v>
       </c>
       <c r="E13" s="5"/>
       <c r="J13" s="13"/>
@@ -15709,8 +15717,8 @@
         <v>31</v>
       </c>
       <c r="C14" s="36">
-        <f>Main!C6/Model!F26</f>
-        <v>98.377551020408163</v>
+        <f>C6/Model!G26</f>
+        <v>-44.775862068965516</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="29"/>
@@ -15727,8 +15735,8 @@
         <v>32</v>
       </c>
       <c r="C15" s="36">
-        <f>C6/Model!G26</f>
-        <v>-66.489655172413791</v>
+        <f>C6/Model!H26</f>
+        <v>-33.552971576227385</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -15736,7 +15744,8 @@
         <v>29</v>
       </c>
       <c r="C16" s="6">
-        <v>1</v>
+        <f>Model!G26/Model!F25-1</f>
+        <v>-8.0047995482283447</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15744,68 +15753,77 @@
         <v>30</v>
       </c>
       <c r="C17" s="6">
-        <f>Model!G26/Model!F26-1</f>
-        <v>-2.4795918367346941</v>
+        <f>Model!H26/Model!G26-1</f>
+        <v>0.33448275862068977</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="L17" s="126" t="s">
-        <v>163</v>
-      </c>
-      <c r="M17" s="126"/>
-      <c r="N17" s="126"/>
+      <c r="L17" s="118" t="s">
+        <v>161</v>
+      </c>
+      <c r="M17" s="118"/>
+      <c r="N17" s="118"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="44">
         <f>C14/(C16*100)</f>
-        <v>0.9837755102040816</v>
+        <v>5.5936268983619329E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
-      </c>
-      <c r="L18" s="127"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="127"/>
+        <v>160</v>
+      </c>
+      <c r="L18" s="119"/>
+      <c r="M18" s="119"/>
+      <c r="N18" s="119"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="44">
         <f>C15/(C17*100)</f>
-        <v>0.2681475805307223</v>
-      </c>
-      <c r="L19" s="127"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="127"/>
+        <v>-1.0031300780521586</v>
+      </c>
+      <c r="E19" t="s">
+        <v>196</v>
+      </c>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" s="6">
-        <f>Model!F7/Model!E7-1</f>
-        <v>3.9205106382978725</v>
-      </c>
-      <c r="L20" s="127"/>
-      <c r="M20" s="127"/>
-      <c r="N20" s="127"/>
+        <f>Model!G29</f>
+        <v>5.2336203669037822</v>
+      </c>
+      <c r="E20" t="s">
+        <v>197</v>
+      </c>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C21" s="6">
-        <f>Model!G7/Model!F7-1</f>
-        <v>1.9057700290577007</v>
-      </c>
-      <c r="L21" s="127"/>
-      <c r="M21" s="127"/>
-      <c r="N21" s="127"/>
+        <f>Model!H29</f>
+        <v>1.8618618618618616</v>
+      </c>
+      <c r="E21" t="s">
+        <v>198</v>
+      </c>
+      <c r="L21" s="119"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
@@ -15815,9 +15833,9 @@
         <f>Model!C13+Model!C11</f>
         <v>0</v>
       </c>
-      <c r="L22" s="127"/>
-      <c r="M22" s="127"/>
-      <c r="N22" s="127"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
@@ -15827,145 +15845,145 @@
         <f>Model!C13</f>
         <v>0</v>
       </c>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="127"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="119"/>
+      <c r="N23" s="119"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="7">
-        <f>Model!C17</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="127"/>
-      <c r="M24" s="127"/>
-      <c r="N24" s="127"/>
+        <f>AVERAGE(Model!R27:R27)</f>
+        <v>0.69916556873078606</v>
+      </c>
+      <c r="L24" s="119"/>
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C25" s="7">
-        <f>Model!C18</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127"/>
+        <f>AVERAGE(Model!O28:R28)</f>
+        <v>0.39784313312429126</v>
+      </c>
+      <c r="L25" s="119"/>
+      <c r="M25" s="119"/>
+      <c r="N25" s="119"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C26" s="36"/>
-      <c r="L26" s="127"/>
-      <c r="M26" s="127"/>
-      <c r="N26" s="127"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="119"/>
+      <c r="N26" s="119"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="113">
-        <f>Model!E56/Model!E64</f>
-        <v>1.8747887020930019E-3</v>
+        <v>68</v>
+      </c>
+      <c r="C27" s="108">
+        <f>C10/Model!R64</f>
+        <v>0.89475851903234216</v>
       </c>
       <c r="E27" t="s">
         <v>59</v>
       </c>
-      <c r="L27" s="127"/>
-      <c r="M27" s="127"/>
-      <c r="N27" s="127"/>
+      <c r="L27" s="119"/>
+      <c r="M27" s="119"/>
+      <c r="N27" s="119"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" s="36" t="e">
         <f>C22/-Model!C11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" t="s">
-        <v>188</v>
-      </c>
-      <c r="L28" s="127"/>
-      <c r="M28" s="127"/>
-      <c r="N28" s="127"/>
+        <v>186</v>
+      </c>
+      <c r="L28" s="119"/>
+      <c r="M28" s="119"/>
+      <c r="N28" s="119"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C29" s="36">
-        <f>Model!E46/Model!E59</f>
+        <f>Model!E45/Model!E58</f>
         <v>9.5958333333333314</v>
       </c>
       <c r="E29" t="s">
-        <v>189</v>
-      </c>
-      <c r="L29" s="127"/>
-      <c r="M29" s="127"/>
-      <c r="N29" s="127"/>
+        <v>187</v>
+      </c>
+      <c r="L29" s="119"/>
+      <c r="M29" s="119"/>
+      <c r="N29" s="119"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C30" s="36">
-        <f>(Model!E40+Model!E41)/Model!E59</f>
+        <f>(Model!E39+Model!E40)/Model!E58</f>
         <v>9.3284090909090907</v>
       </c>
       <c r="E30" t="s">
-        <v>190</v>
-      </c>
-      <c r="L30" s="127"/>
-      <c r="M30" s="127"/>
-      <c r="N30" s="127"/>
+        <v>188</v>
+      </c>
+      <c r="L30" s="119"/>
+      <c r="M30" s="119"/>
+      <c r="N30" s="119"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C31" s="6">
-        <f>(Model!E46-Model!E59)/Model!E54</f>
+        <f>(Model!E45-Model!E58)/Model!E53</f>
         <v>0.63949163050216984</v>
       </c>
-      <c r="L31" s="127"/>
-      <c r="M31" s="127"/>
-      <c r="N31" s="127"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="119"/>
+      <c r="N31" s="119"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C32" s="36"/>
-      <c r="L32" s="127"/>
-      <c r="M32" s="127"/>
-      <c r="N32" s="127"/>
+      <c r="L32" s="119"/>
+      <c r="M32" s="119"/>
+      <c r="N32" s="119"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C33" s="36"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C34" s="38"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C35" s="38"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C36" s="23"/>
     </row>
@@ -15973,25 +15991,25 @@
       <c r="E37" s="10"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="47"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16009,8 +16027,10 @@
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="13"/>
-    <col min="17" max="17" width="11.42578125" style="13"/>
+    <col min="5" max="5" width="11.42578125" style="130"/>
+    <col min="6" max="6" width="11.42578125" style="13"/>
+    <col min="17" max="17" width="11.42578125" style="130"/>
+    <col min="18" max="18" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -16025,14 +16045,17 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="13" t="s">
         <v>54</v>
       </c>
       <c r="G2" t="s">
-        <v>140</v>
+        <v>138</v>
+      </c>
+      <c r="H2" t="s">
+        <v>199</v>
       </c>
       <c r="K2" t="s">
         <v>50</v>
@@ -16041,35 +16064,35 @@
         <v>53</v>
       </c>
       <c r="M2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O2" t="s">
+        <v>139</v>
+      </c>
+      <c r="P2" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q2" s="130" t="s">
         <v>141</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="S2" t="s">
         <v>143</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>144</v>
-      </c>
-      <c r="S2" t="s">
-        <v>145</v>
-      </c>
-      <c r="T2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" s="13">
+        <v>182</v>
+      </c>
+      <c r="E3" s="130">
         <v>117.5</v>
       </c>
       <c r="K3">
@@ -16090,44 +16113,47 @@
       <c r="P3">
         <v>105.1</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="130">
         <v>131.1</v>
+      </c>
+      <c r="R3" s="13">
+        <v>227.7</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M4">
         <v>0.1</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="130">
         <v>0.2</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
+        <v>185</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
       <c r="M5">
         <v>6.3</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="130">
         <v>16.2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+        <v>184</v>
+      </c>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
       <c r="M6">
         <v>-1.4</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="130">
         <v>-1.4</v>
       </c>
     </row>
@@ -16143,17 +16169,19 @@
         <f>SUM(D3:D5)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="131">
         <f t="shared" ref="E7" si="0">SUM(E3:E5)</f>
         <v>117.5</v>
       </c>
-      <c r="F7" s="11">
-        <f>F8</f>
-        <v>578.16</v>
+      <c r="F7" s="14">
+        <f>SUM(O7:R7)</f>
+        <v>534.19999999999993</v>
       </c>
       <c r="G7" s="11">
-        <f>G8</f>
-        <v>1680</v>
+        <v>3330</v>
+      </c>
+      <c r="H7" s="1">
+        <v>9530</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" ref="K7:L7" si="1">SUM(K3:K5)</f>
@@ -16179,13 +16207,13 @@
         <f t="shared" si="2"/>
         <v>105.1</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="131">
         <f>SUM(Q3:Q6)</f>
         <v>146.09999999999997</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>227.7</v>
       </c>
       <c r="S7" s="11">
         <f t="shared" si="2"/>
@@ -16202,12 +16230,15 @@
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="42">
+      <c r="E8" s="140"/>
+      <c r="F8" s="142">
         <v>578.16</v>
       </c>
-      <c r="G8" s="121">
-        <v>1680</v>
+      <c r="G8" s="115">
+        <v>3330</v>
+      </c>
+      <c r="H8">
+        <v>9530</v>
       </c>
       <c r="K8" s="40"/>
       <c r="L8" s="40"/>
@@ -16215,24 +16246,30 @@
       <c r="N8" s="40"/>
       <c r="O8" s="40"/>
       <c r="P8" s="40"/>
-      <c r="Q8" s="13">
+      <c r="Q8" s="130">
         <v>155.72</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="13">
         <v>265.95</v>
+      </c>
+      <c r="S8">
+        <v>401.18</v>
+      </c>
+      <c r="T8">
+        <v>589.63</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="116">
+      <c r="E9" s="140">
         <v>73.400000000000006</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="121"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="139"/>
       <c r="K9" s="40">
         <v>8.9</v>
       </c>
@@ -16251,19 +16288,22 @@
       <c r="P9" s="40">
         <v>30.1</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="Q9" s="130">
         <v>42.9</v>
+      </c>
+      <c r="R9" s="13">
+        <v>68.5</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="121"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="139"/>
       <c r="K10" s="40"/>
       <c r="L10" s="40"/>
       <c r="M10" s="40"/>
@@ -16273,13 +16313,13 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="121"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="139"/>
       <c r="K11" s="40"/>
       <c r="L11" s="40"/>
       <c r="M11" s="40"/>
@@ -16299,13 +16339,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="131">
         <f t="shared" si="3"/>
         <v>73.400000000000006</v>
       </c>
-      <c r="F12" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="F12" s="14">
+        <f>SUM(O12:R12)</f>
+        <v>171</v>
       </c>
       <c r="G12" s="11">
         <f t="shared" si="3"/>
@@ -16335,13 +16375,13 @@
         <f t="shared" si="5"/>
         <v>30.1</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="Q12" s="131">
         <f t="shared" si="5"/>
         <v>42.9</v>
       </c>
-      <c r="R12" s="11">
+      <c r="R12" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="S12" s="11">
         <f t="shared" si="5"/>
@@ -16354,14 +16394,17 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
-      <c r="E13" s="116">
+      <c r="E13" s="140">
         <v>129.69999999999999</v>
       </c>
-      <c r="F13" s="40"/>
+      <c r="F13" s="144">
+        <f>SUM(O13:R13)</f>
+        <v>180.79999999999998</v>
+      </c>
       <c r="K13" s="10">
         <v>25.2</v>
       </c>
@@ -16380,20 +16423,26 @@
       <c r="P13" s="10">
         <v>42.8</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="Q13" s="130">
         <v>44.9</v>
+      </c>
+      <c r="R13" s="13">
+        <v>53.1</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="116">
+      <c r="E14" s="140">
         <v>277.8</v>
       </c>
-      <c r="F14" s="40"/>
+      <c r="F14" s="144">
+        <f>SUM(O14:R14)</f>
+        <v>383.70000000000005</v>
+      </c>
       <c r="K14" s="10">
         <v>51.3</v>
       </c>
@@ -16412,8 +16461,11 @@
       <c r="P14" s="10">
         <v>68.2</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="Q14" s="130">
         <v>89.5</v>
+      </c>
+      <c r="R14" s="13">
+        <v>159.9</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -16422,10 +16474,13 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="15">
+      <c r="E15" s="132">
         <v>80.099999999999994</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="144">
+        <f>SUM(O15:R15)</f>
+        <v>404.1</v>
+      </c>
       <c r="K15" s="10">
         <v>8.9</v>
       </c>
@@ -16444,8 +16499,11 @@
       <c r="P15" s="10">
         <v>75.2</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="Q15" s="130">
         <v>99</v>
+      </c>
+      <c r="R15" s="13">
+        <v>180.7</v>
       </c>
     </row>
     <row r="16" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -16460,17 +16518,17 @@
         <f>D7-SUM(D12:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="131">
         <f>E7-SUM(E12:E15)</f>
         <v>-443.5</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="14">
         <f>F7-SUM(F12:F15)</f>
-        <v>578.16</v>
+        <v>-605.4</v>
       </c>
       <c r="G16" s="11">
         <f>G7-SUM(G12:G15)</f>
-        <v>1680</v>
+        <v>3330</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -16499,13 +16557,13 @@
         <f t="shared" si="6"/>
         <v>-111.20000000000002</v>
       </c>
-      <c r="Q16" s="14">
+      <c r="Q16" s="131">
         <f t="shared" si="6"/>
         <v>-130.20000000000005</v>
       </c>
-      <c r="R16" s="11">
+      <c r="R16" s="14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-234.5</v>
       </c>
       <c r="S16" s="11">
         <f t="shared" si="6"/>
@@ -16518,14 +16576,17 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="15">
+      <c r="E17" s="132">
         <v>63.6</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="144">
+        <f>SUM(O17:R17)</f>
+        <v>-25.9</v>
+      </c>
       <c r="G17" s="10"/>
       <c r="K17" s="10">
         <v>0.4</v>
@@ -16546,11 +16607,14 @@
         <f>3.6-4.8</f>
         <v>-1.1999999999999997</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="132">
         <f>6.2-14.7</f>
         <v>-8.5</v>
       </c>
-      <c r="R17" s="10"/>
+      <c r="R17" s="15">
+        <f>13.5-38.3</f>
+        <v>-24.799999999999997</v>
+      </c>
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
     </row>
@@ -16560,10 +16624,13 @@
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
-      <c r="E18" s="15">
+      <c r="E18" s="132">
         <v>0.4</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="144">
+        <f>SUM(O18:R18)</f>
+        <v>580.9</v>
+      </c>
       <c r="G18" s="10"/>
       <c r="K18" s="10">
         <v>0</v>
@@ -16579,10 +16646,13 @@
       <c r="P18" s="10">
         <v>597.4</v>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="132">
         <v>-7.5</v>
       </c>
-      <c r="R18" s="10"/>
+      <c r="R18" s="15">
+        <f>1.5-10.6</f>
+        <v>-9.1</v>
+      </c>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
@@ -16592,10 +16662,13 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="15">
+      <c r="E19" s="132">
         <v>-17.3</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="144">
+        <f>SUM(O19:R19)</f>
+        <v>74.099999999999994</v>
+      </c>
       <c r="G19" s="10"/>
       <c r="K19" s="10">
         <v>-1</v>
@@ -16616,16 +16689,18 @@
         <f>-6.3+24.6</f>
         <v>18.3</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="132">
         <v>26.3</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="15">
+        <v>21.4</v>
+      </c>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
     </row>
     <row r="20" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C20" s="11">
         <f t="shared" ref="C20:D20" si="7">C16+SUM(C17:C19)</f>
@@ -16635,17 +16710,17 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="131">
         <f t="shared" ref="E20:G20" si="8">E16+SUM(E17:E19)</f>
         <v>-396.8</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="14">
         <f t="shared" si="8"/>
-        <v>578.16</v>
+        <v>23.700000000000045</v>
       </c>
       <c r="G20" s="11">
         <f t="shared" si="8"/>
-        <v>1680</v>
+        <v>3330</v>
       </c>
       <c r="K20" s="11">
         <f t="shared" ref="K20:M20" si="9">K16+SUM(K17:K19)</f>
@@ -16671,13 +16746,13 @@
         <f t="shared" si="10"/>
         <v>503.29999999999984</v>
       </c>
-      <c r="Q20" s="14">
+      <c r="Q20" s="131">
         <f t="shared" ref="Q20:T20" si="11">Q16+SUM(Q17:Q19)</f>
         <v>-119.90000000000005</v>
       </c>
-      <c r="R20" s="11">
+      <c r="R20" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="S20" s="11">
         <f t="shared" si="11"/>
@@ -16694,10 +16769,13 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
-      <c r="E21" s="15">
+      <c r="E21" s="132">
         <v>-0.1</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="144">
+        <f>SUM(O21:R21)</f>
+        <v>4</v>
+      </c>
       <c r="G21" s="10"/>
       <c r="K21" s="10">
         <v>-3</v>
@@ -16717,24 +16795,29 @@
       <c r="P21" s="10">
         <v>0.8</v>
       </c>
-      <c r="Q21" s="15">
+      <c r="Q21" s="132">
         <v>-0.3</v>
       </c>
-      <c r="R21" s="10"/>
+      <c r="R21" s="15">
+        <v>2.6</v>
+      </c>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
-      <c r="E22" s="15">
+      <c r="E22" s="132">
         <f>-465.2-59+772.1</f>
         <v>247.89999999999998</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="144">
+        <f>SUM(O22:R22)</f>
+        <v>-81.900000000000006</v>
+      </c>
       <c r="G22" s="10"/>
       <c r="K22" s="10">
         <v>236</v>
@@ -16748,8 +16831,8 @@
       <c r="P22" s="10">
         <v>-81.900000000000006</v>
       </c>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="10"/>
+      <c r="Q22" s="132"/>
+      <c r="R22" s="15"/>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
     </row>
@@ -16765,17 +16848,17 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="131">
         <f t="shared" ref="E23:G23" si="13">E20-SUM(E21:E22)</f>
         <v>-644.6</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="14">
         <f t="shared" si="13"/>
-        <v>578.16</v>
+        <v>101.60000000000005</v>
       </c>
       <c r="G23" s="11">
         <f t="shared" si="13"/>
-        <v>1680</v>
+        <v>3330</v>
       </c>
       <c r="K23" s="11">
         <f t="shared" ref="K23:M23" si="14">K20-SUM(K21:K22)</f>
@@ -16801,13 +16884,13 @@
         <f t="shared" si="15"/>
         <v>584.39999999999986</v>
       </c>
-      <c r="Q23" s="14">
+      <c r="Q23" s="131">
         <f t="shared" ref="Q23:T23" si="16">Q20-SUM(Q21:Q22)</f>
         <v>-119.60000000000005</v>
       </c>
-      <c r="R23" s="11">
+      <c r="R23" s="14">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>-249.6</v>
       </c>
       <c r="S23" s="11">
         <f t="shared" si="16"/>
@@ -16824,10 +16907,13 @@
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="15">
+      <c r="E24" s="132">
         <v>235.75360000000001</v>
       </c>
-      <c r="F24" s="10"/>
+      <c r="F24" s="144">
+        <f>AVERAGE(O24:R24)</f>
+        <v>245.40952900000002</v>
+      </c>
       <c r="G24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
@@ -16842,10 +16928,12 @@
       <c r="P24" s="10">
         <v>238.70509200000001</v>
       </c>
-      <c r="Q24" s="15">
+      <c r="Q24" s="132">
         <v>251.807222</v>
       </c>
-      <c r="R24" s="10"/>
+      <c r="R24" s="15">
+        <v>253.01697100000001</v>
+      </c>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
     </row>
@@ -16857,17 +16945,17 @@
         <f>C23/C24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D25" s="119" t="e">
+      <c r="D25" s="113" t="e">
         <f>D23/D24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="133">
         <f t="shared" ref="E25:G25" si="17">E23/E24</f>
         <v>-2.7342106334749503</v>
       </c>
-      <c r="F25" s="2" t="e">
+      <c r="F25" s="35">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
+        <v>0.41400185401928724</v>
       </c>
       <c r="G25" s="2" t="e">
         <f t="shared" si="17"/>
@@ -16897,13 +16985,13 @@
         <f t="shared" si="19"/>
         <v>2.4482091902756724</v>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="133">
         <f>Q23/Q24</f>
         <v>-0.47496652022156877</v>
       </c>
-      <c r="R25" s="2" t="e">
+      <c r="R25" s="35">
         <f t="shared" ref="R25:T25" si="20">R23/R24</f>
-        <v>#DIV/0!</v>
+        <v>-0.98649509166719085</v>
       </c>
       <c r="S25" s="2" t="e">
         <f t="shared" si="20"/>
@@ -16920,27 +17008,34 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="43">
+      <c r="E26" s="141"/>
+      <c r="F26" s="145">
         <v>0.98</v>
       </c>
       <c r="G26" s="1">
-        <v>-1.45</v>
-      </c>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="117">
+        <v>-2.9</v>
+      </c>
+      <c r="H26" s="1">
+        <v>-3.87</v>
+      </c>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="134">
         <v>-0.4</v>
       </c>
-      <c r="R26" s="44">
+      <c r="R26" s="111">
         <v>0.22</v>
       </c>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
+      <c r="S26" s="42">
+        <v>-0.63</v>
+      </c>
+      <c r="T26" s="42">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="27" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
@@ -16954,13 +17049,13 @@
         <f>1-D12/D7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="39">
         <f>1-E12/E7</f>
         <v>0.37531914893617013</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="6">
         <f>1-F12/F7</f>
-        <v>1</v>
+        <v>0.67989517034818414</v>
       </c>
       <c r="G27" s="39">
         <f>1-G12/G7</f>
@@ -16990,13 +17085,13 @@
         <f t="shared" si="21"/>
         <v>0.7136060894386298</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="Q27" s="39">
         <f>1-Q12/Q7</f>
         <v>0.70636550308008206</v>
       </c>
-      <c r="R27" s="3" t="e">
+      <c r="R27" s="6">
         <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
+        <v>0.69916556873078606</v>
       </c>
       <c r="S27" s="3" t="e">
         <f t="shared" si="21"/>
@@ -17019,13 +17114,13 @@
         <f>D23/D7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="135">
         <f>E23/E7</f>
         <v>-5.4859574468085111</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="7">
         <f>F23/F7</f>
-        <v>1</v>
+        <v>0.19019093972295031</v>
       </c>
       <c r="G28" s="4">
         <f>G23/G7</f>
@@ -17055,13 +17150,13 @@
         <f t="shared" si="22"/>
         <v>5.5604186489058032</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="Q28" s="135">
         <f>Q23/Q7</f>
         <v>-0.81861738535249884</v>
       </c>
-      <c r="R28" s="4" t="e">
+      <c r="R28" s="7">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>-1.0961791831357048</v>
       </c>
       <c r="S28" s="4" t="e">
         <f t="shared" si="22"/>
@@ -17074,7 +17169,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C29" s="39" t="e">
         <f>C7/#REF!-1</f>
@@ -17084,37 +17179,41 @@
         <f>D7/C7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E29" s="6" t="e">
+      <c r="E29" s="39" t="e">
         <f>E7/D7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F29" s="39">
+      <c r="F29" s="6">
         <f>F7/E7-1</f>
-        <v>3.9205106382978725</v>
+        <v>3.546382978723404</v>
       </c>
       <c r="G29" s="39">
         <f>G7/F7-1</f>
-        <v>1.9057700290577007</v>
+        <v>5.2336203669037822</v>
+      </c>
+      <c r="H29" s="39">
+        <f>H7/G7-1</f>
+        <v>1.8618618618618616</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
-      <c r="O29" s="123">
+      <c r="O29" s="116">
         <f t="shared" ref="O29:T29" si="23">O7/K7-1</f>
         <v>3.8508771929824555</v>
       </c>
-      <c r="P29" s="123">
+      <c r="P29" s="116">
         <f t="shared" si="23"/>
         <v>6.2482758620689651</v>
       </c>
-      <c r="Q29" s="124">
+      <c r="Q29" s="136">
         <f t="shared" si="23"/>
         <v>3.5514018691588776</v>
       </c>
-      <c r="R29" s="4">
+      <c r="R29" s="7">
         <f t="shared" si="23"/>
-        <v>-1</v>
+        <v>5.0079155672823221</v>
       </c>
       <c r="S29" s="4">
         <f t="shared" si="23"/>
@@ -17127,7 +17226,7 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C30" s="4" t="e">
         <f>C13/C7</f>
@@ -17137,13 +17236,13 @@
         <f>D13/D7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="135">
         <f>E13/E7</f>
         <v>1.1038297872340423</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="7">
         <f>F13/F7</f>
-        <v>0</v>
+        <v>0.33845001871958069</v>
       </c>
       <c r="G30" s="4">
         <f>G13/G7</f>
@@ -17173,13 +17272,13 @@
         <f t="shared" si="24"/>
         <v>0.4072312083729781</v>
       </c>
-      <c r="Q30" s="7">
+      <c r="Q30" s="135">
         <f t="shared" si="24"/>
         <v>0.30732375085557845</v>
       </c>
-      <c r="R30" s="4" t="e">
+      <c r="R30" s="7">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
+        <v>0.233201581027668</v>
       </c>
       <c r="S30" s="4" t="e">
         <f t="shared" si="24"/>
@@ -17192,7 +17291,7 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C31" s="4" t="e">
         <f>C14/C7</f>
@@ -17202,13 +17301,13 @@
         <f>D14/D7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="135">
         <f>E14/E7</f>
         <v>2.3642553191489362</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="7">
         <f>F14/F7</f>
-        <v>0</v>
+        <v>0.71827031074503944</v>
       </c>
       <c r="G31" s="4">
         <f>G14/G7</f>
@@ -17238,13 +17337,13 @@
         <f t="shared" si="25"/>
         <v>0.64890580399619413</v>
       </c>
-      <c r="Q31" s="7">
+      <c r="Q31" s="135">
         <f t="shared" si="25"/>
         <v>0.61259411362080785</v>
       </c>
-      <c r="R31" s="4" t="e">
+      <c r="R31" s="7">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>0.70223978919631103</v>
       </c>
       <c r="S31" s="4" t="e">
         <f t="shared" si="25"/>
@@ -17257,7 +17356,7 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C32" s="4" t="e">
         <f>C3/#REF!-1</f>
@@ -17267,11 +17366,11 @@
         <f t="shared" ref="D32:G33" si="26">D3/C3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E32" s="7" t="e">
+      <c r="E32" s="135" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="7">
         <f t="shared" si="26"/>
         <v>-1</v>
       </c>
@@ -17285,14 +17384,14 @@
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="4"/>
+      <c r="Q32" s="135"/>
+      <c r="R32" s="7"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C33" s="4" t="e">
         <f>C4/#REF!-1</f>
@@ -17302,11 +17401,11 @@
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E33" s="7" t="e">
+      <c r="E33" s="135" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F33" s="4" t="e">
+      <c r="F33" s="7" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
@@ -17320,14 +17419,14 @@
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="4"/>
+      <c r="Q33" s="135"/>
+      <c r="R33" s="7"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C34" s="39" t="e">
         <f>C25/#REF!-1</f>
@@ -17337,13 +17436,13 @@
         <f>D25/C25-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E34" s="6" t="e">
+      <c r="E34" s="39" t="e">
         <f>E25/D25-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F34" s="39" t="e">
+      <c r="F34" s="6">
         <f>F25/E25-1</f>
-        <v>#DIV/0!</v>
+        <v>-1.1514154940920283</v>
       </c>
       <c r="G34" s="39" t="e">
         <f>G25/F25-1</f>
@@ -17361,13 +17460,13 @@
         <f t="shared" si="27"/>
         <v>-7.012345679012344</v>
       </c>
-      <c r="Q34" s="7">
+      <c r="Q34" s="135">
         <f t="shared" si="27"/>
         <v>1.7431192660550474</v>
       </c>
-      <c r="R34" s="4">
+      <c r="R34" s="7">
         <f t="shared" si="27"/>
-        <v>-1</v>
+        <v>0.82723279648609038</v>
       </c>
       <c r="S34" s="4">
         <f t="shared" si="27"/>
@@ -17378,921 +17477,919 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="47" t="e">
-        <f>C17/C7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D35" s="47" t="e">
-        <f>D17/D7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E35" s="48">
-        <f>E17/E7</f>
-        <v>0.5412765957446809</v>
-      </c>
-      <c r="F35" s="47">
-        <f>F17/F7</f>
+    <row r="38" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="11">
+        <f t="shared" ref="C38:G38" si="28">C39-C55</f>
         <v>0</v>
       </c>
-      <c r="G35" s="47">
-        <f>G17/G7</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-    </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="49" t="e">
-        <f>-C17/C16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D36" s="47" t="e">
-        <f>-D17/D16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E36" s="48">
-        <f>-E17/E16</f>
-        <v>0.14340473506200677</v>
-      </c>
-      <c r="F36" s="47">
-        <f>-F17/F16</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="47">
-        <f>-G17/G16</f>
-        <v>0</v>
-      </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-    </row>
-    <row r="39" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="11">
-        <f t="shared" ref="C39:G39" si="28">C40-C56</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="11">
+      <c r="D38" s="11">
         <f t="shared" si="28"/>
         <v>109.3</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E38" s="131">
         <f t="shared" si="28"/>
         <v>2443.5</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F38" s="14">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G38" s="11">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="K39" s="11">
-        <f t="shared" ref="K39" si="29">K40-K56</f>
+      <c r="K38" s="11">
+        <f t="shared" ref="K38" si="29">K39-K55</f>
         <v>0</v>
       </c>
-      <c r="L39" s="11">
-        <f t="shared" ref="L39" si="30">L40-L56</f>
+      <c r="L38" s="11">
+        <f t="shared" ref="L38" si="30">L39-L55</f>
         <v>0</v>
       </c>
-      <c r="M39" s="11">
-        <f t="shared" ref="M39" si="31">M40-M56</f>
+      <c r="M38" s="11">
+        <f t="shared" ref="M38" si="31">M39-M55</f>
         <v>0</v>
       </c>
-      <c r="N39" s="11">
-        <f t="shared" ref="N39" si="32">N40-N56</f>
+      <c r="N38" s="11">
+        <f t="shared" ref="N38" si="32">N39-N55</f>
         <v>2443.5</v>
       </c>
-      <c r="O39" s="11">
-        <f t="shared" ref="O39" si="33">O40-O56</f>
+      <c r="O38" s="11">
+        <f t="shared" ref="O38" si="33">O39-O55</f>
         <v>1440.8</v>
       </c>
-      <c r="P39" s="11">
-        <f t="shared" ref="P39" si="34">P40-P56</f>
+      <c r="P38" s="11">
+        <f t="shared" ref="P38" si="34">P39-P55</f>
         <v>1671.3</v>
       </c>
-      <c r="Q39" s="11">
-        <f t="shared" ref="Q39" si="35">Q40-Q56</f>
+      <c r="Q38" s="131">
+        <f t="shared" ref="Q38" si="35">Q39-Q55</f>
         <v>4778.8</v>
       </c>
-      <c r="R39" s="11">
-        <f t="shared" ref="R39" si="36">R40-R56</f>
+      <c r="R38" s="14">
+        <f t="shared" ref="R38" si="36">R39-R55</f>
+        <v>3653.6</v>
+      </c>
+      <c r="S38" s="11">
+        <f t="shared" ref="S38" si="37">S39-S55</f>
         <v>0</v>
       </c>
-      <c r="S39" s="11">
-        <f t="shared" ref="S39" si="37">S40-S56</f>
+      <c r="T38" s="11">
+        <f t="shared" ref="T38" si="38">T39-T55</f>
         <v>0</v>
       </c>
-      <c r="T39" s="11">
-        <f t="shared" ref="T39" si="38">T40-T56</f>
-        <v>0</v>
-      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10">
+        <v>116.1</v>
+      </c>
+      <c r="E39" s="132">
+        <v>2449.6</v>
+      </c>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10">
+        <f>E39</f>
+        <v>2449.6</v>
+      </c>
+      <c r="O39" s="10">
+        <v>1447</v>
+      </c>
+      <c r="P39" s="10">
+        <v>1679.3</v>
+      </c>
+      <c r="Q39" s="132">
+        <v>4794.8</v>
+      </c>
+      <c r="R39" s="15">
+        <v>3678.1</v>
+      </c>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10">
-        <v>116.1</v>
-      </c>
-      <c r="E40" s="15">
-        <v>2449.6</v>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E40" s="130">
+        <v>13.1</v>
       </c>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <f>E40</f>
-        <v>2449.6</v>
+        <f t="shared" ref="N40:N44" si="39">E40</f>
+        <v>13.1</v>
       </c>
       <c r="O40" s="10">
-        <v>1447</v>
+        <v>24.3</v>
       </c>
       <c r="P40" s="10">
-        <v>1679.3</v>
-      </c>
-      <c r="Q40" s="15">
-        <v>4794.8</v>
-      </c>
-      <c r="R40" s="10"/>
+        <v>54.7</v>
+      </c>
+      <c r="Q40" s="132">
+        <v>91.2</v>
+      </c>
+      <c r="R40" s="15">
+        <v>720.3</v>
+      </c>
       <c r="S40" s="10"/>
       <c r="T40" s="10"/>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="E41" s="13">
-        <v>13.1</v>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E41" s="130">
+        <v>22.9</v>
       </c>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <f t="shared" ref="N41:N45" si="39">E41</f>
-        <v>13.1</v>
+        <f t="shared" si="39"/>
+        <v>22.9</v>
       </c>
       <c r="O41" s="10">
-        <v>24.3</v>
+        <v>22.4</v>
       </c>
       <c r="P41" s="10">
-        <v>54.7</v>
-      </c>
-      <c r="Q41" s="15">
-        <v>91.2</v>
-      </c>
-      <c r="R41" s="10"/>
+        <v>28.3</v>
+      </c>
+      <c r="Q41" s="132">
+        <v>29.1</v>
+      </c>
+      <c r="R41" s="15">
+        <v>34.799999999999997</v>
+      </c>
       <c r="S41" s="10"/>
       <c r="T41" s="10"/>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E42" s="13">
-        <v>22.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="E42" s="130">
+        <v>0.6</v>
       </c>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
         <f t="shared" si="39"/>
-        <v>22.9</v>
+        <v>0.6</v>
       </c>
       <c r="O42" s="10">
-        <v>22.4</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="P42" s="10">
-        <v>28.3</v>
-      </c>
-      <c r="Q42" s="15">
-        <v>29.1</v>
-      </c>
-      <c r="R42" s="10"/>
+        <v>74.5</v>
+      </c>
+      <c r="Q42" s="132">
+        <v>107.1</v>
+      </c>
+      <c r="R42" s="15">
+        <v>0</v>
+      </c>
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10">
-        <v>18.8</v>
-      </c>
-      <c r="E43" s="13">
-        <v>0.6</v>
+        <v>5.4</v>
+      </c>
+      <c r="E43" s="130">
+        <v>8.1</v>
       </c>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
         <f t="shared" si="39"/>
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="O43" s="10">
-        <v>80.599999999999994</v>
+        <v>84.4</v>
       </c>
       <c r="P43" s="10">
-        <v>74.5</v>
-      </c>
-      <c r="Q43" s="15">
-        <v>107.1</v>
-      </c>
-      <c r="R43" s="10"/>
+        <v>158.30000000000001</v>
+      </c>
+      <c r="Q43" s="132">
+        <v>133.4</v>
+      </c>
+      <c r="R43" s="15">
+        <v>131.4</v>
+      </c>
       <c r="S43" s="10"/>
       <c r="T43" s="10"/>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10">
-        <v>5.4</v>
-      </c>
-      <c r="E44" s="13">
-        <v>8.1</v>
+        <f>16.9+3289.5</f>
+        <v>3306.4</v>
+      </c>
+      <c r="E44" s="130">
+        <v>39</v>
       </c>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
         <f t="shared" si="39"/>
-        <v>8.1</v>
+        <v>39</v>
       </c>
       <c r="O44" s="10">
-        <v>84.4</v>
+        <v>24.6</v>
       </c>
       <c r="P44" s="10">
-        <v>158.30000000000001</v>
-      </c>
-      <c r="Q44" s="15">
-        <v>133.4</v>
-      </c>
-      <c r="R44" s="10"/>
+        <v>34.5</v>
+      </c>
+      <c r="Q44" s="132">
+        <v>61.4</v>
+      </c>
+      <c r="R44" s="15">
+        <v>146.80000000000001</v>
+      </c>
       <c r="S44" s="10"/>
       <c r="T44" s="10"/>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>148</v>
-      </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10">
-        <f>16.9+3289.5</f>
-        <v>3306.4</v>
-      </c>
-      <c r="E45" s="13">
-        <v>39</v>
-      </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10">
-        <f t="shared" si="39"/>
-        <v>39</v>
-      </c>
-      <c r="O45" s="10">
-        <v>24.6</v>
-      </c>
-      <c r="P45" s="10">
-        <v>34.5</v>
-      </c>
-      <c r="Q45" s="15">
-        <v>61.4</v>
-      </c>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
-    </row>
-    <row r="46" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
+    <row r="45" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="11">
-        <f t="shared" ref="C46:D46" si="40">SUM(C40:C45)</f>
+      <c r="C45" s="11">
+        <f t="shared" ref="C45:D45" si="40">SUM(C39:C44)</f>
         <v>0</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D45" s="11">
         <f t="shared" si="40"/>
         <v>3455.9</v>
       </c>
-      <c r="E46" s="14">
-        <f t="shared" ref="E46:G46" si="41">SUM(E40:E45)</f>
+      <c r="E45" s="131">
+        <f t="shared" ref="E45:G45" si="41">SUM(E39:E44)</f>
         <v>2533.2999999999997</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F45" s="14">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G45" s="11">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="K46" s="11">
-        <f t="shared" ref="K46:M46" si="42">SUM(K40:K45)</f>
+      <c r="K45" s="11">
+        <f t="shared" ref="K45:M45" si="42">SUM(K39:K44)</f>
         <v>0</v>
       </c>
-      <c r="L46" s="11">
+      <c r="L45" s="11">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="M46" s="11">
+      <c r="M45" s="11">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="N46" s="11">
-        <f t="shared" ref="N46:P46" si="43">SUM(N40:N45)</f>
+      <c r="N45" s="11">
+        <f t="shared" ref="N45:P45" si="43">SUM(N39:N44)</f>
         <v>2533.2999999999997</v>
       </c>
-      <c r="O46" s="11">
+      <c r="O45" s="11">
         <f t="shared" si="43"/>
         <v>1683.3</v>
       </c>
-      <c r="P46" s="11">
+      <c r="P45" s="11">
         <f t="shared" si="43"/>
         <v>2029.6</v>
       </c>
-      <c r="Q46" s="14">
-        <f t="shared" ref="Q46:T46" si="44">SUM(Q40:Q45)</f>
+      <c r="Q45" s="131">
+        <f t="shared" ref="Q45:T45" si="44">SUM(Q39:Q44)</f>
         <v>5217</v>
       </c>
-      <c r="R46" s="11">
+      <c r="R45" s="14">
+        <f t="shared" si="44"/>
+        <v>4711.3999999999996</v>
+      </c>
+      <c r="S45" s="11">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="S46" s="11">
+      <c r="T45" s="11">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="T46" s="11">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10">
+        <v>132.4</v>
+      </c>
+      <c r="E46" s="132">
+        <v>847</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10">
+        <f t="shared" ref="N46:N52" si="45">E46</f>
+        <v>847</v>
+      </c>
+      <c r="O46" s="10">
+        <v>1334.1</v>
+      </c>
+      <c r="P46" s="10">
+        <v>1789.4</v>
+      </c>
+      <c r="Q46" s="132">
+        <v>3314.4</v>
+      </c>
+      <c r="R46" s="15">
+        <v>5572.5</v>
+      </c>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="10">
-        <v>132.4</v>
-      </c>
-      <c r="E47" s="15">
-        <v>847</v>
-      </c>
-      <c r="F47" s="10"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E47" s="132">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F47" s="15"/>
       <c r="G47" s="10"/>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <f t="shared" ref="N47:N53" si="45">E47</f>
-        <v>847</v>
+        <f t="shared" si="45"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="O47" s="10">
-        <v>1334.1</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="P47" s="10">
-        <v>1789.4</v>
-      </c>
-      <c r="Q47" s="15">
-        <v>3314.4</v>
-      </c>
-      <c r="R47" s="10"/>
+        <v>15.6</v>
+      </c>
+      <c r="Q47" s="132">
+        <v>18</v>
+      </c>
+      <c r="R47" s="15">
+        <v>19.7</v>
+      </c>
       <c r="S47" s="10"/>
       <c r="T47" s="10"/>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E48" s="15">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F48" s="10"/>
+        <v>18.7</v>
+      </c>
+      <c r="E48" s="132">
+        <v>45</v>
+      </c>
+      <c r="F48" s="15"/>
       <c r="G48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
         <f t="shared" si="45"/>
-        <v>4.9000000000000004</v>
+        <v>45</v>
       </c>
       <c r="O48" s="10">
-        <v>17.399999999999999</v>
+        <v>250.3</v>
       </c>
       <c r="P48" s="10">
-        <v>15.6</v>
-      </c>
-      <c r="Q48" s="15">
-        <v>18</v>
-      </c>
-      <c r="R48" s="10"/>
+        <v>277.3</v>
+      </c>
+      <c r="Q48" s="132">
+        <v>501</v>
+      </c>
+      <c r="R48" s="15">
+        <v>918.8</v>
+      </c>
       <c r="S48" s="10"/>
       <c r="T48" s="10"/>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10">
-        <v>18.7</v>
-      </c>
-      <c r="E49" s="15">
-        <v>45</v>
-      </c>
-      <c r="F49" s="10"/>
+        <v>6.4</v>
+      </c>
+      <c r="E49" s="132">
+        <v>6.4</v>
+      </c>
+      <c r="F49" s="15"/>
       <c r="G49" s="10"/>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
         <f t="shared" si="45"/>
-        <v>45</v>
+        <v>6.4</v>
       </c>
       <c r="O49" s="10">
-        <v>250.3</v>
+        <v>6.4</v>
       </c>
       <c r="P49" s="10">
-        <v>277.3</v>
-      </c>
-      <c r="Q49" s="15">
-        <v>501</v>
-      </c>
-      <c r="R49" s="10"/>
+        <v>32.299999999999997</v>
+      </c>
+      <c r="Q49" s="132">
+        <v>21.7</v>
+      </c>
+      <c r="R49" s="15">
+        <v>11.1</v>
+      </c>
       <c r="S49" s="10"/>
       <c r="T49" s="10"/>
     </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10">
-        <v>6.4</v>
-      </c>
-      <c r="E50" s="15">
-        <v>6.4</v>
-      </c>
-      <c r="F50" s="10"/>
+        <v>90.7</v>
+      </c>
+      <c r="E50" s="132">
+        <v>90.7</v>
+      </c>
+      <c r="F50" s="15"/>
       <c r="G50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
         <f t="shared" si="45"/>
-        <v>6.4</v>
+        <v>90.7</v>
       </c>
       <c r="O50" s="10">
-        <v>6.4</v>
+        <v>90.7</v>
       </c>
       <c r="P50" s="10">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="Q50" s="15">
-        <v>21.7</v>
-      </c>
-      <c r="R50" s="10"/>
+        <v>835.1</v>
+      </c>
+      <c r="Q50" s="132">
+        <v>835.1</v>
+      </c>
+      <c r="R50" s="15">
+        <v>836.6</v>
+      </c>
       <c r="S50" s="10"/>
       <c r="T50" s="10"/>
     </row>
     <row r="51" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10">
-        <v>90.7</v>
-      </c>
-      <c r="E51" s="15">
-        <v>90.7</v>
-      </c>
-      <c r="F51" s="10"/>
+        <v>5.2</v>
+      </c>
+      <c r="E51" s="132">
+        <v>7.8</v>
+      </c>
+      <c r="F51" s="15"/>
       <c r="G51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
         <f t="shared" si="45"/>
-        <v>90.7</v>
+        <v>7.8</v>
       </c>
       <c r="O51" s="10">
-        <v>90.7</v>
+        <v>8.9</v>
       </c>
       <c r="P51" s="10">
-        <v>835.1</v>
-      </c>
-      <c r="Q51" s="15">
-        <v>835.1</v>
-      </c>
-      <c r="R51" s="10"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Q51" s="132">
+        <v>9</v>
+      </c>
+      <c r="R51" s="15">
+        <v>11.8</v>
+      </c>
       <c r="S51" s="10"/>
       <c r="T51" s="10"/>
     </row>
     <row r="52" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10">
-        <v>5.2</v>
-      </c>
-      <c r="E52" s="15">
-        <v>7.8</v>
-      </c>
-      <c r="F52" s="10"/>
+        <f>11.6+5035.9</f>
+        <v>5047.5</v>
+      </c>
+      <c r="E52" s="132">
+        <v>13.5</v>
+      </c>
+      <c r="F52" s="15"/>
       <c r="G52" s="10"/>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
         <f t="shared" si="45"/>
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="O52" s="10">
-        <v>8.9</v>
+        <v>45.4</v>
       </c>
       <c r="P52" s="10">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="Q52" s="15">
-        <v>9</v>
-      </c>
-      <c r="R52" s="10"/>
+        <v>108.5</v>
+      </c>
+      <c r="Q52" s="132">
+        <v>186</v>
+      </c>
+      <c r="R52" s="15">
+        <v>367.9</v>
+      </c>
       <c r="S52" s="10"/>
       <c r="T52" s="10"/>
     </row>
-    <row r="53" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>152</v>
-      </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10">
-        <f>11.6+5035.9</f>
-        <v>5047.5</v>
-      </c>
-      <c r="E53" s="15">
-        <v>13.5</v>
-      </c>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10">
-        <f t="shared" si="45"/>
-        <v>13.5</v>
-      </c>
-      <c r="O53" s="10">
-        <v>45.4</v>
-      </c>
-      <c r="P53" s="10">
-        <v>108.5</v>
-      </c>
-      <c r="Q53" s="15">
-        <v>186</v>
-      </c>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-    </row>
-    <row r="54" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
+    <row r="53" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="11">
-        <f>SUM(C46:C53)</f>
+      <c r="C53" s="11">
+        <f>SUM(C45:C52)</f>
         <v>0</v>
       </c>
-      <c r="D54" s="11">
-        <f>SUM(D46:D53)</f>
+      <c r="D53" s="11">
+        <f>SUM(D45:D52)</f>
         <v>8761.4</v>
       </c>
-      <c r="E54" s="14">
-        <f>SUM(E46:E53)</f>
+      <c r="E53" s="131">
+        <f>SUM(E45:E52)</f>
         <v>3548.6</v>
       </c>
-      <c r="F54" s="11">
-        <f>SUM(F46:F53)</f>
+      <c r="F53" s="14">
+        <f>SUM(F45:F52)</f>
         <v>0</v>
       </c>
-      <c r="G54" s="11">
-        <f>SUM(G46:G53)</f>
+      <c r="G53" s="11">
+        <f>SUM(G45:G52)</f>
         <v>0</v>
       </c>
-      <c r="K54" s="11">
-        <f t="shared" ref="K54:T54" si="46">SUM(K46:K53)</f>
+      <c r="K53" s="11">
+        <f t="shared" ref="K53:T53" si="46">SUM(K45:K52)</f>
         <v>0</v>
       </c>
-      <c r="L54" s="11">
+      <c r="L53" s="11">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="M54" s="11">
+      <c r="M53" s="11">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="N54" s="11">
+      <c r="N53" s="11">
         <f t="shared" si="46"/>
         <v>3548.6</v>
       </c>
-      <c r="O54" s="11">
+      <c r="O53" s="11">
         <f t="shared" si="46"/>
         <v>3436.5</v>
       </c>
-      <c r="P54" s="11">
+      <c r="P53" s="11">
         <f t="shared" si="46"/>
         <v>5096.6000000000004</v>
       </c>
-      <c r="Q54" s="14">
+      <c r="Q53" s="131">
         <f t="shared" si="46"/>
         <v>10102.200000000001</v>
       </c>
-      <c r="R54" s="11">
+      <c r="R53" s="14">
+        <f t="shared" si="46"/>
+        <v>12449.8</v>
+      </c>
+      <c r="S53" s="11">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="S54" s="11">
+      <c r="T53" s="11">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="T54" s="11">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10">
+        <v>57.2</v>
+      </c>
+      <c r="E54" s="132">
+        <v>235.5</v>
+      </c>
+      <c r="F54" s="15"/>
+      <c r="G54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10">
+        <f t="shared" ref="N54:N57" si="47">E54</f>
+        <v>235.5</v>
+      </c>
+      <c r="O54" s="10">
+        <v>61.4</v>
+      </c>
+      <c r="P54" s="10">
+        <v>103.6</v>
+      </c>
+      <c r="Q54" s="132">
+        <v>726.4</v>
+      </c>
+      <c r="R54" s="15">
+        <v>1210.0999999999999</v>
+      </c>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10">
-        <v>57.2</v>
-      </c>
-      <c r="E55" s="15">
-        <v>235.5</v>
-      </c>
-      <c r="F55" s="10"/>
+        <v>6.8</v>
+      </c>
+      <c r="E55" s="132">
+        <v>6.1</v>
+      </c>
+      <c r="F55" s="15"/>
       <c r="G55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <f t="shared" ref="N55:N58" si="47">E55</f>
-        <v>235.5</v>
+        <f t="shared" si="47"/>
+        <v>6.1</v>
       </c>
       <c r="O55" s="10">
-        <v>61.4</v>
+        <v>6.2</v>
       </c>
       <c r="P55" s="10">
-        <v>103.6</v>
-      </c>
-      <c r="Q55" s="15">
-        <v>726.4</v>
-      </c>
-      <c r="R55" s="10"/>
+        <v>8</v>
+      </c>
+      <c r="Q55" s="132">
+        <v>16</v>
+      </c>
+      <c r="R55" s="15">
+        <v>24.5</v>
+      </c>
       <c r="S55" s="10"/>
       <c r="T55" s="10"/>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10">
-        <v>6.8</v>
-      </c>
-      <c r="E56" s="15">
-        <v>6.1</v>
-      </c>
-      <c r="F56" s="10"/>
+        <v>8.1</v>
+      </c>
+      <c r="E56" s="132">
+        <v>5.9</v>
+      </c>
+      <c r="F56" s="15"/>
       <c r="G56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
         <f t="shared" si="47"/>
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="O56" s="10">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="P56" s="10">
-        <v>8</v>
-      </c>
-      <c r="Q56" s="15">
-        <v>16</v>
-      </c>
-      <c r="R56" s="10"/>
+        <v>7.2</v>
+      </c>
+      <c r="Q56" s="132">
+        <v>36.6</v>
+      </c>
+      <c r="R56" s="15">
+        <v>17.7</v>
+      </c>
       <c r="S56" s="10"/>
       <c r="T56" s="10"/>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10">
-        <v>8.1</v>
-      </c>
-      <c r="E57" s="15">
-        <v>5.9</v>
-      </c>
-      <c r="F57" s="10"/>
+        <f>6.9+3791</f>
+        <v>3797.9</v>
+      </c>
+      <c r="E57" s="132">
+        <v>16.5</v>
+      </c>
+      <c r="F57" s="15"/>
       <c r="G57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
         <f t="shared" si="47"/>
-        <v>5.9</v>
+        <v>16.5</v>
       </c>
       <c r="O57" s="10">
-        <v>6.9</v>
+        <v>19</v>
       </c>
       <c r="P57" s="10">
-        <v>7.2</v>
-      </c>
-      <c r="Q57" s="15">
-        <v>36.6</v>
-      </c>
-      <c r="R57" s="10"/>
+        <v>19.3</v>
+      </c>
+      <c r="Q57" s="132">
+        <v>15.6</v>
+      </c>
+      <c r="R57" s="15">
+        <v>275.5</v>
+      </c>
       <c r="S57" s="10"/>
       <c r="T57" s="10"/>
     </row>
-    <row r="58" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10">
-        <f>6.9+3791</f>
-        <v>3797.9</v>
-      </c>
-      <c r="E58" s="15">
-        <v>16.5</v>
-      </c>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10">
-        <f t="shared" si="47"/>
-        <v>16.5</v>
-      </c>
-      <c r="O58" s="10">
-        <v>19</v>
-      </c>
-      <c r="P58" s="10">
-        <v>19.3</v>
-      </c>
-      <c r="Q58" s="15">
-        <v>15.6</v>
-      </c>
-      <c r="R58" s="10"/>
-      <c r="S58" s="10"/>
-      <c r="T58" s="10"/>
-    </row>
-    <row r="59" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="1" t="s">
+    <row r="58" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="11">
-        <f>SUM(C55:C58)</f>
+      <c r="C58" s="11">
+        <f>SUM(C54:C57)</f>
         <v>0</v>
       </c>
-      <c r="D59" s="11">
-        <f>SUM(D55:D58)</f>
+      <c r="D58" s="11">
+        <f>SUM(D54:D57)</f>
         <v>3870</v>
       </c>
-      <c r="E59" s="14">
-        <f>SUM(E55:E58)</f>
+      <c r="E58" s="131">
+        <f>SUM(E54:E57)</f>
         <v>264</v>
       </c>
-      <c r="F59" s="11">
-        <f>SUM(F55:F58)</f>
+      <c r="F58" s="14">
+        <f>SUM(F54:F57)</f>
         <v>0</v>
       </c>
-      <c r="G59" s="11">
-        <f>SUM(G55:G58)</f>
+      <c r="G58" s="11">
+        <f>SUM(G54:G57)</f>
         <v>0</v>
       </c>
-      <c r="K59" s="11">
-        <f t="shared" ref="K59:T59" si="48">SUM(K55:K58)</f>
+      <c r="K58" s="11">
+        <f t="shared" ref="K58:T58" si="48">SUM(K54:K57)</f>
         <v>0</v>
       </c>
-      <c r="L59" s="11">
+      <c r="L58" s="11">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="M59" s="11">
+      <c r="M58" s="11">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="N59" s="11">
-        <f t="shared" si="48"/>
+      <c r="N58" s="11">
+        <f>SUM(N54:N57)</f>
         <v>264</v>
       </c>
-      <c r="O59" s="11">
-        <f t="shared" si="48"/>
+      <c r="O58" s="11">
+        <f>SUM(O54:O57)</f>
         <v>93.5</v>
       </c>
-      <c r="P59" s="11">
+      <c r="P58" s="11">
         <f t="shared" si="48"/>
         <v>138.1</v>
       </c>
-      <c r="Q59" s="14">
+      <c r="Q58" s="131">
         <f t="shared" si="48"/>
         <v>794.6</v>
       </c>
-      <c r="R59" s="11">
+      <c r="R58" s="14">
+        <f t="shared" si="48"/>
+        <v>1527.8</v>
+      </c>
+      <c r="S58" s="11">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="S59" s="11">
+      <c r="T58" s="11">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="T59" s="11">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
+    </row>
+    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E59" s="132">
+        <v>30.3</v>
+      </c>
+      <c r="F59" s="15"/>
+      <c r="G59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10">
+        <f t="shared" ref="N59:N62" si="49">E59</f>
+        <v>30.3</v>
+      </c>
+      <c r="O59" s="10">
+        <v>181.6</v>
+      </c>
+      <c r="P59" s="10">
+        <v>204.5</v>
+      </c>
+      <c r="Q59" s="132">
+        <v>405.4</v>
+      </c>
+      <c r="R59" s="15">
+        <v>760.5</v>
+      </c>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>49</v>
+        <v>189</v>
       </c>
       <c r="C60" s="10"/>
-      <c r="D60" s="10">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="E60" s="15">
-        <v>30.3</v>
-      </c>
-      <c r="F60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="132"/>
+      <c r="F60" s="15"/>
       <c r="G60" s="10"/>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
       <c r="M60" s="10"/>
-      <c r="N60" s="10">
-        <f t="shared" ref="N60:N62" si="49">E60</f>
-        <v>30.3</v>
-      </c>
-      <c r="O60" s="10">
-        <v>181.6</v>
-      </c>
-      <c r="P60" s="10">
-        <v>204.5</v>
-      </c>
-      <c r="Q60" s="15">
-        <v>405.4</v>
-      </c>
-      <c r="R60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="132">
+        <v>4090.8</v>
+      </c>
+      <c r="R60" s="15">
+        <v>4103.2</v>
+      </c>
       <c r="S60" s="10"/>
       <c r="T60" s="10"/>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="10"/>
+      <c r="E61" s="132"/>
+      <c r="F61" s="15"/>
       <c r="G61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
@@ -18300,26 +18397,26 @@
       <c r="N61" s="10"/>
       <c r="O61" s="10"/>
       <c r="P61" s="10"/>
-      <c r="Q61" s="15">
-        <v>4090.8</v>
-      </c>
-      <c r="R61" s="10"/>
+      <c r="Q61" s="132"/>
+      <c r="R61" s="15">
+        <v>1302</v>
+      </c>
       <c r="S61" s="10"/>
       <c r="T61" s="10"/>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10">
         <f>0.2+1580.9</f>
         <v>1581.1000000000001</v>
       </c>
-      <c r="E62" s="15">
+      <c r="E62" s="132">
         <v>0.6</v>
       </c>
-      <c r="F62" s="10"/>
+      <c r="F62" s="15"/>
       <c r="G62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
@@ -18335,10 +18432,12 @@
         <f>978.2+0.3</f>
         <v>978.5</v>
       </c>
-      <c r="Q62" s="15">
+      <c r="Q62" s="132">
         <v>0.6</v>
       </c>
-      <c r="R62" s="10"/>
+      <c r="R62" s="15">
+        <v>143.1</v>
+      </c>
       <c r="S62" s="10"/>
       <c r="T62" s="10"/>
     </row>
@@ -18347,27 +18446,27 @@
         <v>19</v>
       </c>
       <c r="C63" s="11">
-        <f>SUM(C59:C62)</f>
+        <f>SUM(C58:C62)</f>
         <v>0</v>
       </c>
       <c r="D63" s="11">
-        <f>SUM(D59:D62)</f>
+        <f>SUM(D58:D62)</f>
         <v>5460.8</v>
       </c>
-      <c r="E63" s="14">
-        <f>SUM(E59:E62)</f>
+      <c r="E63" s="131">
+        <f>SUM(E58:E62)</f>
         <v>294.90000000000003</v>
       </c>
-      <c r="F63" s="11">
-        <f>SUM(F59:F62)</f>
+      <c r="F63" s="14">
+        <f>SUM(F58:F62)</f>
         <v>0</v>
       </c>
       <c r="G63" s="11">
-        <f>SUM(G59:G62)</f>
+        <f>SUM(G58:G62)</f>
         <v>0</v>
       </c>
       <c r="K63" s="11">
-        <f t="shared" ref="K63:T63" si="50">SUM(K59:K62)</f>
+        <f t="shared" ref="K63:T63" si="50">SUM(K58:K62)</f>
         <v>0</v>
       </c>
       <c r="L63" s="11">
@@ -18390,13 +18489,13 @@
         <f t="shared" si="50"/>
         <v>1321.1</v>
       </c>
-      <c r="Q63" s="14">
+      <c r="Q63" s="131">
         <f t="shared" si="50"/>
         <v>5291.4000000000005</v>
       </c>
-      <c r="R63" s="11">
+      <c r="R63" s="14">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>7836.6</v>
       </c>
       <c r="S63" s="11">
         <f t="shared" si="50"/>
@@ -18412,27 +18511,27 @@
         <v>64</v>
       </c>
       <c r="C64" s="10">
-        <f>C54-C63</f>
+        <f>C53-C63</f>
         <v>0</v>
       </c>
       <c r="D64" s="10">
-        <f>D54-D63</f>
+        <f>D53-D63</f>
         <v>3300.5999999999995</v>
       </c>
-      <c r="E64" s="15">
-        <f>E54-E63</f>
+      <c r="E64" s="132">
+        <f>E53-E63</f>
         <v>3253.7</v>
       </c>
-      <c r="F64" s="10">
-        <f>F54-F63</f>
+      <c r="F64" s="15">
+        <f>F53-F63</f>
         <v>0</v>
       </c>
       <c r="G64" s="10">
-        <f>G54-G63</f>
+        <f>G53-G63</f>
         <v>0</v>
       </c>
       <c r="K64" s="10">
-        <f t="shared" ref="K64:T64" si="51">K54-K63</f>
+        <f t="shared" ref="K64:T64" si="51">K53-K63</f>
         <v>0</v>
       </c>
       <c r="L64" s="10">
@@ -18455,13 +18554,13 @@
         <f t="shared" si="51"/>
         <v>3775.5000000000005</v>
       </c>
-      <c r="Q64" s="15">
+      <c r="Q64" s="132">
         <f t="shared" si="51"/>
         <v>4810.8</v>
       </c>
-      <c r="R64" s="10">
+      <c r="R64" s="15">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>4613.1999999999989</v>
       </c>
       <c r="S64" s="10">
         <f t="shared" si="51"/>
@@ -18472,22 +18571,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" s="50"/>
-      <c r="D66" s="120"/>
-      <c r="E66" s="16"/>
-      <c r="Q66" s="16"/>
-    </row>
-    <row r="84" spans="5:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="41"/>
-      <c r="Q84" s="41"/>
-    </row>
-    <row r="85" spans="5:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="16"/>
-      <c r="Q85" s="16"/>
+        <v>65</v>
+      </c>
+      <c r="C66" s="45"/>
+      <c r="D66" s="114"/>
+      <c r="E66" s="137"/>
+      <c r="F66" s="16"/>
+      <c r="Q66" s="137"/>
+      <c r="R66" s="16"/>
+    </row>
+    <row r="84" spans="5:18" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E84" s="138"/>
+      <c r="F84" s="41"/>
+      <c r="Q84" s="138"/>
+      <c r="R84" s="41"/>
+    </row>
+    <row r="85" spans="5:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E85" s="137"/>
+      <c r="F85" s="16"/>
+      <c r="Q85" s="137"/>
+      <c r="R85" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -18509,43 +18614,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="118">
+      <c r="B1" s="112">
         <v>45413</v>
       </c>
-      <c r="C1" s="118">
+      <c r="C1" s="112">
         <v>45444</v>
       </c>
-      <c r="D1" s="118">
+      <c r="D1" s="112">
         <v>45474</v>
       </c>
-      <c r="E1" s="118">
+      <c r="E1" s="112">
         <v>45505</v>
       </c>
-      <c r="F1" s="118">
+      <c r="F1" s="112">
         <v>45536</v>
       </c>
-      <c r="G1" s="118">
+      <c r="G1" s="112">
         <v>45566</v>
       </c>
-      <c r="H1" s="118">
+      <c r="H1" s="112">
         <v>45597</v>
       </c>
-      <c r="I1" s="118">
+      <c r="I1" s="112">
         <v>45627</v>
       </c>
-      <c r="J1" s="118">
+      <c r="J1" s="112">
         <v>45658</v>
       </c>
-      <c r="K1" s="118">
+      <c r="K1" s="112">
         <v>45689</v>
       </c>
-      <c r="L1" s="118">
+      <c r="L1" s="112">
         <v>45717</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -18559,7 +18664,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -18573,7 +18678,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -18587,7 +18692,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -18601,7 +18706,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -18615,12 +18720,12 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I10">
         <v>80</v>
@@ -18634,7 +18739,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I11">
         <v>90</v>
@@ -18648,7 +18753,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I12">
         <v>40</v>
@@ -27050,51 +27155,51 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="128" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="130"/>
+        <v>78</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="122"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" t="e">
         <f>C2/C3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H2" s="54"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="56"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D3" t="e">
         <f t="shared" ref="D3:D66" si="0">C3/C4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="K3" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="L3" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="60" t="s">
+      <c r="M3" s="56" t="s">
         <v>85</v>
-      </c>
-      <c r="L3" s="60" t="s">
-        <v>86</v>
-      </c>
-      <c r="M3" s="61" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -27102,27 +27207,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H4" s="62" t="e">
+      <c r="H4" s="57" t="e">
         <f>$I$19-3*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I4" s="63" t="e">
+      <c r="I4" s="58" t="e">
         <f>H4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="59">
         <f>COUNTIF(D:D,"&lt;="&amp;H4)</f>
         <v>67</v>
       </c>
-      <c r="K4" s="64" t="e">
+      <c r="K4" s="59" t="e">
         <f>"Less than "&amp;TEXT(H4,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L4" s="65" t="e">
+      <c r="L4" s="60" t="e">
         <f>J4/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M4" s="66" t="e">
+      <c r="M4" s="61" t="e">
         <f>L4</f>
         <v>#DIV/0!</v>
       </c>
@@ -27132,27 +27237,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="67" t="e">
+      <c r="H5" s="62" t="e">
         <f>$I$19-2.4*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I5" s="68" t="e">
+      <c r="I5" s="63" t="e">
         <f>H5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J5" s="69">
+      <c r="J5" s="64">
         <f>COUNTIFS(D:D,"&lt;="&amp;H5,D:D,"&gt;"&amp;H4)</f>
         <v>67</v>
       </c>
-      <c r="K5" s="70" t="e">
+      <c r="K5" s="65" t="e">
         <f t="shared" ref="K5:K14" si="1">TEXT(H4,"0,00%")&amp;" to "&amp;TEXT(H5,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L5" s="71" t="e">
+      <c r="L5" s="66" t="e">
         <f>J5/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M5" s="72" t="e">
+      <c r="M5" s="67" t="e">
         <f>M4+L5</f>
         <v>#DIV/0!</v>
       </c>
@@ -27162,27 +27267,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H6" s="67" t="e">
+      <c r="H6" s="62" t="e">
         <f>$I$19-1.8*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I6" s="68" t="e">
+      <c r="I6" s="63" t="e">
         <f t="shared" ref="I6:I14" si="2">H6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J6" s="69">
+      <c r="J6" s="64">
         <f t="shared" ref="J6:J14" si="3">COUNTIFS(D:D,"&lt;="&amp;H6,D:D,"&gt;"&amp;H5)</f>
         <v>67</v>
       </c>
-      <c r="K6" s="70" t="e">
+      <c r="K6" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L6" s="71" t="e">
+      <c r="L6" s="66" t="e">
         <f t="shared" ref="L6:L15" si="4">J6/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M6" s="72" t="e">
+      <c r="M6" s="67" t="e">
         <f t="shared" ref="M6:M15" si="5">M5+L6</f>
         <v>#DIV/0!</v>
       </c>
@@ -27192,27 +27297,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H7" s="67" t="e">
+      <c r="H7" s="62" t="e">
         <f>$I$19-1.2*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I7" s="68" t="e">
+      <c r="I7" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K7" s="70" t="e">
+      <c r="K7" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L7" s="71" t="e">
+      <c r="L7" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M7" s="72" t="e">
+      <c r="M7" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27222,27 +27327,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H8" s="67" t="e">
+      <c r="H8" s="62" t="e">
         <f>$I$19-0.6*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I8" s="68" t="e">
+      <c r="I8" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J8" s="69">
+      <c r="J8" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K8" s="70" t="e">
+      <c r="K8" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L8" s="71" t="e">
+      <c r="L8" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M8" s="72" t="e">
+      <c r="M8" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27252,27 +27357,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="67" t="e">
+      <c r="H9" s="62" t="e">
         <f>$I$19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="68" t="e">
+      <c r="I9" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="69">
+      <c r="J9" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K9" s="70" t="e">
+      <c r="K9" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="71" t="e">
+      <c r="L9" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M9" s="72" t="e">
+      <c r="M9" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27282,27 +27387,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="67" t="e">
+      <c r="H10" s="62" t="e">
         <f>$I$19+0.6*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="68" t="e">
+      <c r="I10" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J10" s="69">
+      <c r="J10" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K10" s="70" t="e">
+      <c r="K10" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L10" s="71" t="e">
+      <c r="L10" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="72" t="e">
+      <c r="M10" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27312,27 +27417,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H11" s="67" t="e">
+      <c r="H11" s="62" t="e">
         <f>$I$19+1.2*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="68" t="e">
+      <c r="I11" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J11" s="69">
+      <c r="J11" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K11" s="70" t="e">
+      <c r="K11" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="71" t="e">
+      <c r="L11" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M11" s="72" t="e">
+      <c r="M11" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27342,27 +27447,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H12" s="67" t="e">
+      <c r="H12" s="62" t="e">
         <f>$I$19+1.8*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12" s="68" t="e">
+      <c r="I12" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K12" s="70" t="e">
+      <c r="K12" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L12" s="71" t="e">
+      <c r="L12" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M12" s="72" t="e">
+      <c r="M12" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27372,27 +27477,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="67" t="e">
+      <c r="H13" s="62" t="e">
         <f>$I$19+2.4*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I13" s="68" t="e">
+      <c r="I13" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J13" s="69">
+      <c r="J13" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K13" s="70" t="e">
+      <c r="K13" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L13" s="71" t="e">
+      <c r="L13" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M13" s="72" t="e">
+      <c r="M13" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27402,27 +27507,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H14" s="67" t="e">
+      <c r="H14" s="62" t="e">
         <f>$I$19+3*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I14" s="68" t="e">
+      <c r="I14" s="63" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="69">
+      <c r="J14" s="64">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K14" s="70" t="e">
+      <c r="K14" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L14" s="71" t="e">
+      <c r="L14" s="66" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M14" s="72" t="e">
+      <c r="M14" s="67" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27432,23 +27537,23 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="73"/>
-      <c r="I15" s="74" t="s">
-        <v>88</v>
-      </c>
-      <c r="J15" s="74">
+      <c r="H15" s="68"/>
+      <c r="I15" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="69">
         <f>COUNTIF(D:D,"&gt;"&amp;H14)</f>
         <v>67</v>
       </c>
-      <c r="K15" s="74" t="e">
+      <c r="K15" s="69" t="e">
         <f>"Greater than "&amp;TEXT(H14,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L15" s="75" t="e">
+      <c r="L15" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M15" s="75" t="e">
+      <c r="M15" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27458,350 +27563,350 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="76"/>
-      <c r="M16" s="77"/>
+      <c r="H16" s="71"/>
+      <c r="M16" s="72"/>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D17" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="131" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="132"/>
-      <c r="M17" s="77"/>
+      <c r="H17" s="123" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="124"/>
+      <c r="M17" s="72"/>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="133"/>
-      <c r="I18" s="134"/>
-      <c r="M18" s="77"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126"/>
+      <c r="M18" s="72"/>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D19" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="78" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="114" t="e">
+      <c r="H19" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="109" t="e">
         <f>AVERAGE(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M19" s="77"/>
+      <c r="M19" s="72"/>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D20" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="78" t="s">
-        <v>90</v>
-      </c>
-      <c r="I20" s="114" t="e">
+      <c r="H20" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="109" t="e">
         <f>_xlfn.STDEV.S(D:D)/SQRT(COUNT(D:D))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M20" s="77"/>
+      <c r="M20" s="72"/>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D21" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" s="78" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" s="114" t="e">
+      <c r="H21" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="109" t="e">
         <f>MEDIAN(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M21" s="77"/>
+      <c r="M21" s="72"/>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D22" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H22" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" s="114" t="e">
+      <c r="H22" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="109" t="e">
         <f>MODE(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M22" s="77"/>
+      <c r="M22" s="72"/>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D23" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="114" t="e">
+      <c r="H23" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="109" t="e">
         <f>_xlfn.STDEV.S(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M23" s="77"/>
+      <c r="M23" s="72"/>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D24" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24" s="78" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="114" t="e">
+      <c r="H24" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="109" t="e">
         <f>_xlfn.VAR.S(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M24" s="77"/>
+      <c r="M24" s="72"/>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D25" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H25" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="I25" s="115" t="e">
+      <c r="H25" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="110" t="e">
         <f>KURT(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M25" s="77"/>
+      <c r="M25" s="72"/>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D26" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="78" t="s">
-        <v>96</v>
-      </c>
-      <c r="I26" s="115" t="e">
+      <c r="H26" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="110" t="e">
         <f>SKEW(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M26" s="77"/>
+      <c r="M26" s="72"/>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D27" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="78" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27" s="114" t="e">
+      <c r="H27" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="109" t="e">
         <f>I29-I28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M27" s="77"/>
+      <c r="M27" s="72"/>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D28" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H28" s="78" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" s="114" t="e">
+      <c r="H28" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" s="109" t="e">
         <f>MIN(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M28" s="77"/>
+      <c r="M28" s="72"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D29" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="78" t="s">
-        <v>98</v>
-      </c>
-      <c r="I29" s="114" t="e">
+      <c r="H29" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="109" t="e">
         <f>MAX(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M29" s="77"/>
+      <c r="M29" s="72"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="78" t="s">
-        <v>99</v>
-      </c>
-      <c r="I30" s="115" t="e">
+      <c r="H30" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="110" t="e">
         <f>SUM(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M30" s="77"/>
+      <c r="M30" s="72"/>
     </row>
     <row r="31" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D31" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="79" t="s">
-        <v>100</v>
-      </c>
-      <c r="I31" s="56">
+      <c r="H31" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="I31" s="51">
         <f>COUNT(D:D)</f>
         <v>0</v>
       </c>
-      <c r="M31" s="77"/>
+      <c r="M31" s="72"/>
     </row>
     <row r="32" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D32" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="81"/>
-      <c r="M32" s="77"/>
+      <c r="H32" s="76"/>
+      <c r="M32" s="72"/>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D33" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="82"/>
-      <c r="I33" s="83" t="s">
+      <c r="H33" s="77"/>
+      <c r="I33" s="78" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="K33" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="L33" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="J33" s="83" t="s">
-        <v>100</v>
-      </c>
-      <c r="K33" s="83" t="s">
-        <v>102</v>
-      </c>
-      <c r="L33" s="84" t="s">
-        <v>103</v>
-      </c>
-      <c r="M33" s="77"/>
+      <c r="M33" s="72"/>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D34" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="71" t="e">
+      <c r="H34" s="80" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="66" t="e">
         <f>AVERAGEIF(D:D,"&gt;0")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J34" s="69">
+      <c r="J34" s="64">
         <f>COUNTIF(D:D,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="K34" s="71" t="e">
+      <c r="K34" s="66" t="e">
         <f>J34/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L34" s="72" t="e">
+      <c r="L34" s="67" t="e">
         <f>K34*I34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M34" s="77"/>
+      <c r="M34" s="72"/>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D35" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="85" t="s">
-        <v>105</v>
-      </c>
-      <c r="I35" s="71" t="e">
+      <c r="H35" s="80" t="s">
+        <v>103</v>
+      </c>
+      <c r="I35" s="66" t="e">
         <f>AVERAGEIF(D:D,"&lt;0")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J35" s="69">
+      <c r="J35" s="64">
         <f>COUNTIF(D:D,"&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="K35" s="71" t="e">
+      <c r="K35" s="66" t="e">
         <f>J35/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L35" s="72" t="e">
+      <c r="L35" s="67" t="e">
         <f t="shared" ref="L35:L36" si="6">K35*I35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M35" s="77"/>
+      <c r="M35" s="72"/>
     </row>
     <row r="36" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D36" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="86" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="74">
+      <c r="H36" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="69">
         <v>0</v>
       </c>
-      <c r="J36" s="74">
+      <c r="J36" s="69">
         <f>COUNTIF(D:D,"0")</f>
         <v>0</v>
       </c>
-      <c r="K36" s="87" t="e">
+      <c r="K36" s="82" t="e">
         <f>J36/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L36" s="75" t="e">
+      <c r="L36" s="70" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M36" s="77"/>
+      <c r="M36" s="72"/>
     </row>
     <row r="37" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D37" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H37" s="81"/>
-      <c r="I37" s="88"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="77"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="83"/>
+      <c r="M37" s="72"/>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D38" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H38" s="62" t="s">
+      <c r="H38" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="J38" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="I38" s="83" t="s">
+      <c r="K38" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="J38" s="83" t="s">
+      <c r="L38" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="K38" s="83" t="s">
+      <c r="M38" s="79" t="s">
         <v>110</v>
-      </c>
-      <c r="L38" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="M38" s="84" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.25">
@@ -27809,26 +27914,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="89">
+      <c r="H39" s="84">
         <v>1</v>
       </c>
-      <c r="I39" s="71" t="e">
+      <c r="I39" s="66" t="e">
         <f>$I$19+($H39*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J39" s="71" t="e">
+      <c r="J39" s="66" t="e">
         <f>$I$19-($H39*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K39" s="69">
+      <c r="K39" s="64">
         <f>COUNTIFS(D:D,"&lt;"&amp;I39,D:D,"&gt;"&amp;J39)</f>
         <v>67</v>
       </c>
-      <c r="L39" s="71" t="e">
+      <c r="L39" s="66" t="e">
         <f>K39/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M39" s="72">
+      <c r="M39" s="67">
         <v>0.68269999999999997</v>
       </c>
     </row>
@@ -27837,26 +27942,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="89">
+      <c r="H40" s="84">
         <v>2</v>
       </c>
-      <c r="I40" s="71" t="e">
+      <c r="I40" s="66" t="e">
         <f>$I$19+($H40*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="71" t="e">
+      <c r="J40" s="66" t="e">
         <f>$I$19-($H40*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K40" s="69">
+      <c r="K40" s="64">
         <f>COUNTIFS(D:D,"&lt;"&amp;I40,D:D,"&gt;"&amp;J40)</f>
         <v>67</v>
       </c>
-      <c r="L40" s="71" t="e">
+      <c r="L40" s="66" t="e">
         <f>K40/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M40" s="72">
+      <c r="M40" s="67">
         <v>0.95450000000000002</v>
       </c>
     </row>
@@ -27865,26 +27970,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="89">
+      <c r="H41" s="84">
         <v>3</v>
       </c>
-      <c r="I41" s="71" t="e">
+      <c r="I41" s="66" t="e">
         <f>$I$19+($H41*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="71" t="e">
+      <c r="J41" s="66" t="e">
         <f>$I$19-($H41*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K41" s="69">
+      <c r="K41" s="64">
         <f>COUNTIFS(D:D,"&lt;"&amp;I41,D:D,"&gt;"&amp;J41)</f>
         <v>67</v>
       </c>
-      <c r="L41" s="71" t="e">
+      <c r="L41" s="66" t="e">
         <f>K41/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M41" s="90">
+      <c r="M41" s="85">
         <v>0.99729999999999996</v>
       </c>
     </row>
@@ -27893,46 +27998,46 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H42" s="67"/>
-      <c r="M42" s="90"/>
+      <c r="H42" s="62"/>
+      <c r="M42" s="85"/>
     </row>
     <row r="43" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D43" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H43" s="135" t="s">
-        <v>113</v>
-      </c>
-      <c r="I43" s="136"/>
-      <c r="J43" s="136"/>
-      <c r="K43" s="136"/>
-      <c r="L43" s="136"/>
-      <c r="M43" s="137"/>
+      <c r="H43" s="127" t="s">
+        <v>111</v>
+      </c>
+      <c r="I43" s="128"/>
+      <c r="J43" s="128"/>
+      <c r="K43" s="128"/>
+      <c r="L43" s="128"/>
+      <c r="M43" s="129"/>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D44" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H44" s="91">
+      <c r="H44" s="86">
         <v>0.01</v>
       </c>
-      <c r="I44" s="92" t="e">
+      <c r="I44" s="87" t="e">
         <f t="shared" ref="I44:I58" si="7">_xlfn.PERCENTILE.INC(D:D,H44)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J44" s="93">
+      <c r="J44" s="88">
         <v>0.2</v>
       </c>
-      <c r="K44" s="92" t="e">
+      <c r="K44" s="87" t="e">
         <f t="shared" ref="K44:K56" si="8">_xlfn.PERCENTILE.INC(D:D,J44)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L44" s="93">
+      <c r="L44" s="88">
         <v>0.85</v>
       </c>
-      <c r="M44" s="94" t="e">
+      <c r="M44" s="89" t="e">
         <f t="shared" ref="M44:M58" si="9">_xlfn.PERCENTILE.INC(D:D,L44)</f>
         <v>#DIV/0!</v>
       </c>
@@ -27942,24 +28047,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H45" s="95">
+      <c r="H45" s="90">
         <v>0.02</v>
       </c>
-      <c r="I45" s="96" t="e">
+      <c r="I45" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J45" s="97">
+      <c r="J45" s="92">
         <v>0.25</v>
       </c>
-      <c r="K45" s="96" t="e">
+      <c r="K45" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L45" s="97">
+      <c r="L45" s="92">
         <v>0.86</v>
       </c>
-      <c r="M45" s="98" t="e">
+      <c r="M45" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -27969,24 +28074,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H46" s="95">
+      <c r="H46" s="90">
         <v>0.03</v>
       </c>
-      <c r="I46" s="96" t="e">
+      <c r="I46" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J46" s="97">
+      <c r="J46" s="92">
         <v>0.3</v>
       </c>
-      <c r="K46" s="96" t="e">
+      <c r="K46" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L46" s="97">
+      <c r="L46" s="92">
         <v>0.87</v>
       </c>
-      <c r="M46" s="98" t="e">
+      <c r="M46" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -27996,24 +28101,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H47" s="95">
+      <c r="H47" s="90">
         <v>0.04</v>
       </c>
-      <c r="I47" s="96" t="e">
+      <c r="I47" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J47" s="97">
+      <c r="J47" s="92">
         <v>0.35</v>
       </c>
-      <c r="K47" s="96" t="e">
+      <c r="K47" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L47" s="97">
+      <c r="L47" s="92">
         <v>0.88</v>
       </c>
-      <c r="M47" s="98" t="e">
+      <c r="M47" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28023,24 +28128,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H48" s="95">
+      <c r="H48" s="90">
         <v>0.05</v>
       </c>
-      <c r="I48" s="96" t="e">
+      <c r="I48" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J48" s="97">
+      <c r="J48" s="92">
         <v>0.4</v>
       </c>
-      <c r="K48" s="96" t="e">
+      <c r="K48" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L48" s="97">
+      <c r="L48" s="92">
         <v>0.89</v>
       </c>
-      <c r="M48" s="98" t="e">
+      <c r="M48" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28050,24 +28155,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H49" s="95">
+      <c r="H49" s="90">
         <v>0.06</v>
       </c>
-      <c r="I49" s="96" t="e">
+      <c r="I49" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J49" s="97">
+      <c r="J49" s="92">
         <v>0.45</v>
       </c>
-      <c r="K49" s="96" t="e">
+      <c r="K49" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L49" s="97">
+      <c r="L49" s="92">
         <v>0.9</v>
       </c>
-      <c r="M49" s="98" t="e">
+      <c r="M49" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28077,24 +28182,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H50" s="95">
+      <c r="H50" s="90">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I50" s="96" t="e">
+      <c r="I50" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J50" s="97">
+      <c r="J50" s="92">
         <v>0.5</v>
       </c>
-      <c r="K50" s="96" t="e">
+      <c r="K50" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L50" s="97">
+      <c r="L50" s="92">
         <v>0.91</v>
       </c>
-      <c r="M50" s="98" t="e">
+      <c r="M50" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28104,24 +28209,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H51" s="95">
+      <c r="H51" s="90">
         <v>0.08</v>
       </c>
-      <c r="I51" s="96" t="e">
+      <c r="I51" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J51" s="97">
+      <c r="J51" s="92">
         <v>0.55000000000000004</v>
       </c>
-      <c r="K51" s="96" t="e">
+      <c r="K51" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L51" s="97">
+      <c r="L51" s="92">
         <v>0.92</v>
       </c>
-      <c r="M51" s="98" t="e">
+      <c r="M51" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28131,24 +28236,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H52" s="95">
+      <c r="H52" s="90">
         <v>0.09</v>
       </c>
-      <c r="I52" s="96" t="e">
+      <c r="I52" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J52" s="97">
+      <c r="J52" s="92">
         <v>0.6</v>
       </c>
-      <c r="K52" s="96" t="e">
+      <c r="K52" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L52" s="97">
+      <c r="L52" s="92">
         <v>0.93</v>
       </c>
-      <c r="M52" s="98" t="e">
+      <c r="M52" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28158,24 +28263,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H53" s="95">
+      <c r="H53" s="90">
         <v>0.1</v>
       </c>
-      <c r="I53" s="96" t="e">
+      <c r="I53" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J53" s="97">
+      <c r="J53" s="92">
         <v>0.65</v>
       </c>
-      <c r="K53" s="96" t="e">
+      <c r="K53" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L53" s="97">
+      <c r="L53" s="92">
         <v>0.94</v>
       </c>
-      <c r="M53" s="98" t="e">
+      <c r="M53" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28185,24 +28290,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H54" s="95">
+      <c r="H54" s="90">
         <v>0.11</v>
       </c>
-      <c r="I54" s="96" t="e">
+      <c r="I54" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J54" s="97">
+      <c r="J54" s="92">
         <v>0.7</v>
       </c>
-      <c r="K54" s="96" t="e">
+      <c r="K54" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L54" s="97">
+      <c r="L54" s="92">
         <v>0.95</v>
       </c>
-      <c r="M54" s="98" t="e">
+      <c r="M54" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28212,24 +28317,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H55" s="95">
+      <c r="H55" s="90">
         <v>0.12</v>
       </c>
-      <c r="I55" s="96" t="e">
+      <c r="I55" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J55" s="97">
+      <c r="J55" s="92">
         <v>0.75</v>
       </c>
-      <c r="K55" s="96" t="e">
+      <c r="K55" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L55" s="97">
+      <c r="L55" s="92">
         <v>0.96</v>
       </c>
-      <c r="M55" s="98" t="e">
+      <c r="M55" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28239,24 +28344,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H56" s="95">
+      <c r="H56" s="90">
         <v>0.13</v>
       </c>
-      <c r="I56" s="96" t="e">
+      <c r="I56" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J56" s="97">
+      <c r="J56" s="92">
         <v>0.8</v>
       </c>
-      <c r="K56" s="96" t="e">
+      <c r="K56" s="91" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L56" s="97">
+      <c r="L56" s="92">
         <v>0.97</v>
       </c>
-      <c r="M56" s="98" t="e">
+      <c r="M56" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28266,19 +28371,19 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H57" s="95">
+      <c r="H57" s="90">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I57" s="96" t="e">
+      <c r="I57" s="91" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J57" s="97"/>
-      <c r="K57" s="96"/>
-      <c r="L57" s="97">
+      <c r="J57" s="92"/>
+      <c r="K57" s="91"/>
+      <c r="L57" s="92">
         <v>0.98</v>
       </c>
-      <c r="M57" s="98" t="e">
+      <c r="M57" s="93" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28288,19 +28393,19 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H58" s="99">
+      <c r="H58" s="94">
         <v>0.15</v>
       </c>
-      <c r="I58" s="100" t="e">
+      <c r="I58" s="95" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J58" s="101"/>
-      <c r="K58" s="80"/>
-      <c r="L58" s="102">
+      <c r="J58" s="96"/>
+      <c r="K58" s="75"/>
+      <c r="L58" s="97">
         <v>0.99</v>
       </c>
-      <c r="M58" s="103" t="e">
+      <c r="M58" s="98" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28316,47 +28421,47 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H60" s="104" t="s">
-        <v>114</v>
-      </c>
-      <c r="I60" s="105"/>
+      <c r="H60" s="99" t="s">
+        <v>112</v>
+      </c>
+      <c r="I60" s="100"/>
     </row>
     <row r="61" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D61" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H61" s="106" t="s">
-        <v>115</v>
-      </c>
-      <c r="I61" s="107"/>
+      <c r="H61" s="101" t="s">
+        <v>113</v>
+      </c>
+      <c r="I61" s="102"/>
     </row>
     <row r="62" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D62" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H62" s="108"/>
+      <c r="H62" s="103"/>
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H63" s="104" t="s">
-        <v>116</v>
-      </c>
-      <c r="I63" s="109"/>
+      <c r="H63" s="99" t="s">
+        <v>114</v>
+      </c>
+      <c r="I63" s="104"/>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D64" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H64" s="110" t="s">
-        <v>117</v>
-      </c>
-      <c r="I64" s="111">
+      <c r="H64" s="105" t="s">
+        <v>115</v>
+      </c>
+      <c r="I64" s="106">
         <f>I63*(1-I60)</f>
         <v>0</v>
       </c>
@@ -28366,10 +28471,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H65" s="106" t="s">
-        <v>118</v>
-      </c>
-      <c r="I65" s="112">
+      <c r="H65" s="101" t="s">
+        <v>116</v>
+      </c>
+      <c r="I65" s="107">
         <f>I63*(1+I61)</f>
         <v>0</v>
       </c>
